--- a/Movies and Music.xlsx
+++ b/Movies and Music.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kroon\.gemini\antigravity\playground\Books Movies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BF8770-56EB-4769-B0B9-9543B1F60BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA758C-C043-405E-8552-6DF3D5F68BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movies" sheetId="1" r:id="rId1"/>
     <sheet name="TV" sheetId="5" r:id="rId2"/>
     <sheet name="Books" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movies!$A$1:$F$432</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="559">
   <si>
     <t>Rating</t>
   </si>
@@ -1704,6 +1705,21 @@
   </si>
   <si>
     <t>Director</t>
+  </si>
+  <si>
+    <t>Loose Change</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>PG</t>
   </si>
 </sst>
 </file>
@@ -8897,7 +8913,7 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -8916,4 +8932,48 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CA9B39-F148-4282-B30F-098DCE817F14}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Movies and Music.xlsx
+++ b/Movies and Music.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kroon\.gemini\antigravity\playground\Books Movies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA758C-C043-405E-8552-6DF3D5F68BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756E1F0A-F264-4123-BAE6-E5718EE90EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Movies" sheetId="1" r:id="rId1"/>
     <sheet name="TV" sheetId="5" r:id="rId2"/>
     <sheet name="Books" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
+    <sheet name="Misc" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movies!$A$1:$F$432</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="560">
   <si>
     <t>Rating</t>
   </si>
@@ -1719,7 +1719,10 @@
     <t>Link</t>
   </si>
   <si>
-    <t>PG</t>
+    <t>Everything is a Rich Man's Trick</t>
+  </si>
+  <si>
+    <t>Tin Foil</t>
   </si>
 </sst>
 </file>
@@ -8936,10 +8939,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CA9B39-F148-4282-B30F-098DCE817F14}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.85546875" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
   </cols>
@@ -8959,18 +8962,16 @@
       <c r="A2" t="s">
         <v>554</v>
       </c>
-      <c r="B2">
-        <v>911</v>
+      <c r="B2" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>558</v>
+      </c>
       <c r="B3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/Movies and Music.xlsx
+++ b/Movies and Music.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kroon\.gemini\antigravity\playground\Books Movies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756E1F0A-F264-4123-BAE6-E5718EE90EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5CF50F-3B0F-49C4-AD19-E68ABFA3DD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movies" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Misc" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movies!$A$1:$F$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movies!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TV!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="559">
   <si>
     <t>Rating</t>
   </si>
@@ -609,9 +609,6 @@
     <t>The Wizard of Oz</t>
   </si>
   <si>
-    <t>Pirates of the Caribbean: The Curse of the Black Pearl</t>
-  </si>
-  <si>
     <t>Blade Runner</t>
   </si>
   <si>
@@ -942,9 +939,6 @@
     <t>From Dusk Till Dawn</t>
   </si>
   <si>
-    <t>Borat: Cultural Learnings of America for Make Benefit Glorious Nation of Kazakhstan</t>
-  </si>
-  <si>
     <t>Jerry Maguire</t>
   </si>
   <si>
@@ -1398,9 +1392,6 @@
     <t xml:space="preserve">Michael was best </t>
   </si>
   <si>
-    <t>Speak No Evil</t>
-  </si>
-  <si>
     <t>1917</t>
   </si>
   <si>
@@ -1476,9 +1467,6 @@
     <t>Artsy underclass</t>
   </si>
   <si>
-    <t>Crawdad</t>
-  </si>
-  <si>
     <t>Eat, Pray, Love, Murder. Predictable</t>
   </si>
   <si>
@@ -1584,9 +1572,6 @@
     <t>The Menu</t>
   </si>
   <si>
-    <t>Rich people making movies decrying rich people… and a girl boss. Story fine. Hollywood, blah</t>
-  </si>
-  <si>
     <t>Golden Turd Award</t>
   </si>
   <si>
@@ -1686,15 +1671,9 @@
     <t>Warriors</t>
   </si>
   <si>
-    <t>TMNT</t>
-  </si>
-  <si>
     <t>unrated</t>
   </si>
   <si>
-    <t>Woke Trope</t>
-  </si>
-  <si>
     <t>Got weird</t>
   </si>
   <si>
@@ -1723,6 +1702,24 @@
   </si>
   <si>
     <t>Tin Foil</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Borat</t>
+  </si>
+  <si>
+    <t>Spacey got weirder</t>
+  </si>
+  <si>
+    <t>Pirates of the Caribbean: Black Pearl</t>
+  </si>
+  <si>
+    <t>Crawdads Sing</t>
+  </si>
+  <si>
+    <t>Rich actors pretending to dislike the rich</t>
   </si>
 </sst>
 </file>
@@ -2129,20 +2126,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F440"/>
+  <dimension ref="A1:F438"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2154,727 +2151,778 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>1968</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B3">
-        <v>1980</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>269</v>
       </c>
       <c r="B4">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>245</v>
       </c>
       <c r="B5">
-        <v>1972</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>441</v>
       </c>
       <c r="B6">
-        <v>1974</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>9.9</v>
+        <v>6.5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>506</v>
       </c>
       <c r="B7">
-        <v>1979</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>9.9</v>
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>417</v>
       </c>
       <c r="B8">
-        <v>1981</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>9.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="B9">
-        <v>1982</v>
+        <v>2024</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>435</v>
       </c>
       <c r="B10">
-        <v>1985</v>
+        <v>2024</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>410</v>
       </c>
       <c r="B11">
-        <v>1986</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>270</v>
       </c>
       <c r="B12">
-        <v>1987</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12">
-        <v>9.9</v>
+        <v>4.5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="B13">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13">
-        <v>9.9</v>
+        <v>4.5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="B14">
-        <v>1993</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14">
-        <v>9.9</v>
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>442</v>
       </c>
       <c r="B15">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15">
-        <v>9.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>274</v>
+        <v>96</v>
       </c>
       <c r="B16">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16">
-        <v>9.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B17">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17">
-        <v>9.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B18">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
       <c r="D18">
-        <v>9.9</v>
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>525</v>
       </c>
       <c r="B19">
-        <v>2002</v>
+        <v>2022</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="F19" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>271</v>
       </c>
       <c r="B20">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20">
-        <v>9.9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>544</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>268</v>
       </c>
       <c r="B21">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>9.6999999999999993</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>508</v>
       </c>
       <c r="B22">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22">
-        <v>9.6</v>
+        <v>5.5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B23">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23">
-        <v>9.6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B24">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
       </c>
       <c r="D24">
-        <v>9.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>413</v>
       </c>
       <c r="B25">
-        <v>1983</v>
+        <v>2022</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>557</v>
       </c>
       <c r="B26">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="B27">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27">
-        <v>9.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>356</v>
+        <v>144</v>
       </c>
       <c r="B28">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D28">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>391</v>
+        <v>252</v>
       </c>
       <c r="B29">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>409</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30">
-        <v>10</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="B31">
-        <v>1939</v>
+        <v>2020</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>534</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B32">
-        <v>1975</v>
+        <v>2020</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="D32">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="B33">
-        <v>1977</v>
+        <v>2019</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B34">
-        <v>1980</v>
+        <v>2019</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="B35">
-        <v>1984</v>
+        <v>2019</v>
       </c>
       <c r="C35" t="s">
         <v>36</v>
       </c>
       <c r="D35">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="B36">
-        <v>1984</v>
+        <v>2019</v>
       </c>
       <c r="C36" t="s">
         <v>36</v>
       </c>
       <c r="D36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="B37">
-        <v>1986</v>
+        <v>2019</v>
       </c>
       <c r="C37" t="s">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>348</v>
       </c>
       <c r="B38">
-        <v>1987</v>
+        <v>2019</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
       </c>
       <c r="D38">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>169</v>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="B39">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="C39" t="s">
         <v>36</v>
       </c>
-      <c r="D39">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D39" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="B40">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>371</v>
       </c>
       <c r="B41">
-        <v>1991</v>
+        <v>2019</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="B42">
-        <v>1991</v>
+        <v>2018</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B43">
-        <v>1992</v>
+        <v>2018</v>
       </c>
       <c r="C43" t="s">
         <v>36</v>
       </c>
       <c r="D43">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="B44">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
       </c>
       <c r="D44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
       </c>
       <c r="D45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>334</v>
       </c>
       <c r="B46">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
       </c>
       <c r="D46">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>307</v>
+        <v>192</v>
       </c>
       <c r="B47">
-        <v>1998</v>
+        <v>2018</v>
       </c>
       <c r="C47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>352</v>
+      </c>
+      <c r="B48">
+        <v>2018</v>
+      </c>
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>231</v>
+      </c>
+      <c r="B49">
+        <v>2018</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>304</v>
+      </c>
+      <c r="B50">
+        <v>2018</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50">
+        <v>4.5</v>
+      </c>
+      <c r="F50" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>354</v>
+      </c>
+      <c r="B51">
+        <v>2017</v>
+      </c>
+      <c r="C51" t="s">
         <v>27</v>
       </c>
-      <c r="D47">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48">
-        <v>1999</v>
-      </c>
-      <c r="C48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49">
-        <v>1999</v>
-      </c>
-      <c r="C49" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50">
-        <v>2000</v>
-      </c>
-      <c r="C50" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>141</v>
-      </c>
-      <c r="B51">
-        <v>2003</v>
-      </c>
-      <c r="C51" t="s">
-        <v>36</v>
-      </c>
       <c r="D51">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="B52">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C52" t="s">
         <v>36</v>
@@ -2883,79 +2931,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B53">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C53" t="s">
         <v>36</v>
       </c>
       <c r="D53">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="B54">
-        <v>2006</v>
+        <v>2017</v>
       </c>
       <c r="C54" t="s">
         <v>36</v>
       </c>
       <c r="D54">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>319</v>
       </c>
       <c r="B55">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C55" t="s">
         <v>36</v>
       </c>
       <c r="D55">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+      <c r="F55" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
       <c r="B56">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
       </c>
       <c r="D56">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>207</v>
       </c>
       <c r="B57">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D57">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="B58">
         <v>2017</v>
@@ -2964,183 +3015,198 @@
         <v>36</v>
       </c>
       <c r="D58">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F58" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>308</v>
+        <v>184</v>
       </c>
       <c r="B59">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F59" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>543</v>
+        <v>8</v>
       </c>
       <c r="B60">
-        <v>1988</v>
+        <v>2017</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="B61">
-        <v>1989</v>
+        <v>2016</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
       </c>
       <c r="D61">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="B62">
-        <v>1995</v>
+        <v>2016</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
       <c r="D62">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>318</v>
+        <v>397</v>
       </c>
       <c r="B63">
-        <v>1995</v>
+        <v>2016</v>
       </c>
       <c r="C63" t="s">
         <v>36</v>
       </c>
       <c r="D63">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="B64">
-        <v>1995</v>
+        <v>2016</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D64">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="B65">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="C65" t="s">
         <v>36</v>
       </c>
       <c r="D65">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B66">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="C66" t="s">
         <v>36</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="B67">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
       </c>
       <c r="D67">
-        <v>8.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="B68">
-        <v>2003</v>
+        <v>2016</v>
       </c>
       <c r="C68" t="s">
         <v>36</v>
       </c>
       <c r="D68">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="F68" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="B69">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69">
-        <v>8.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="B70">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C70" t="s">
         <v>36</v>
       </c>
-      <c r="D70">
-        <v>8</v>
-      </c>
+      <c r="D70" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="B71">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C71" t="s">
         <v>36</v>
@@ -3148,252 +3214,251 @@
       <c r="D71">
         <v>8</v>
       </c>
-      <c r="F71" t="s">
-        <v>224</v>
-      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>438</v>
+        <v>68</v>
       </c>
       <c r="B72">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="C72" t="s">
         <v>36</v>
       </c>
       <c r="D72">
-        <v>8.5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>439</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>484</v>
+        <v>60</v>
       </c>
       <c r="B73">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="C73" t="s">
         <v>36</v>
       </c>
       <c r="D73">
-        <v>8.5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>485</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>530</v>
+        <v>405</v>
       </c>
       <c r="B74">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C74" t="s">
         <v>36</v>
       </c>
       <c r="D74">
-        <v>8.5</v>
-      </c>
-      <c r="F74" t="s">
-        <v>531</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="B75">
-        <v>1979</v>
+        <v>2015</v>
       </c>
       <c r="C75" t="s">
         <v>36</v>
       </c>
       <c r="D75">
-        <v>8.3000000000000007</v>
+        <v>7</v>
+      </c>
+      <c r="F75" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>396</v>
+        <v>148</v>
       </c>
       <c r="B76">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C76" t="s">
         <v>36</v>
       </c>
       <c r="D76">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="F76" t="s">
-        <v>463</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="B77">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C77" t="s">
         <v>36</v>
       </c>
       <c r="D77">
-        <v>8.3000000000000007</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="B78">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C78" t="s">
         <v>36</v>
       </c>
       <c r="D78">
-        <v>8.3000000000000007</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="B79">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="C79" t="s">
         <v>36</v>
       </c>
       <c r="D79">
-        <v>8.3000000000000007</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>421</v>
+        <v>340</v>
+      </c>
+      <c r="B80">
+        <v>2015</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
-      </c>
-      <c r="D80">
-        <v>8.3000000000000007</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="B81">
-        <v>1960</v>
+        <v>2015</v>
       </c>
       <c r="C81" t="s">
         <v>36</v>
       </c>
-      <c r="D81">
-        <v>8</v>
-      </c>
+      <c r="D81" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="B82">
-        <v>1962</v>
+        <v>2015</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
-      </c>
-      <c r="D82">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>263</v>
       </c>
       <c r="B83">
-        <v>1966</v>
+        <v>2015</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83">
-        <v>8</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>283</v>
       </c>
       <c r="B84">
-        <v>1971</v>
+        <v>2015</v>
       </c>
       <c r="C84" t="s">
         <v>36</v>
       </c>
-      <c r="D84">
-        <v>8</v>
+      <c r="D84" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="B85">
-        <v>1975</v>
+        <v>2014</v>
       </c>
       <c r="C85" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>363</v>
+        <v>97</v>
       </c>
       <c r="B86">
-        <v>1976</v>
+        <v>2014</v>
       </c>
       <c r="C86" t="s">
         <v>36</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="B87">
-        <v>1979</v>
+        <v>2014</v>
       </c>
       <c r="C87" t="s">
         <v>36</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>161</v>
+        <v>299</v>
       </c>
       <c r="B88">
-        <v>1987</v>
+        <v>2014</v>
       </c>
       <c r="C88" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D88">
         <v>8</v>
@@ -3401,10 +3466,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B89">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
@@ -3415,10 +3480,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>343</v>
+        <v>193</v>
       </c>
       <c r="B90">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C90" t="s">
         <v>36</v>
@@ -3426,460 +3491,465 @@
       <c r="D90">
         <v>8</v>
       </c>
-      <c r="F90" t="s">
-        <v>453</v>
-      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
       <c r="B91">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C91" t="s">
         <v>36</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="B92">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C92" t="s">
         <v>36</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="B93">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C93" t="s">
         <v>36</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B94">
-        <v>1991</v>
+        <v>2014</v>
       </c>
       <c r="C94" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="B95">
-        <v>1991</v>
+        <v>2014</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F95" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B96">
-        <v>1993</v>
+        <v>2014</v>
       </c>
       <c r="C96" t="s">
         <v>36</v>
       </c>
       <c r="D96">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>35</v>
+        <v>243</v>
       </c>
       <c r="B97">
-        <v>1994</v>
+        <v>2014</v>
       </c>
       <c r="C97" t="s">
         <v>36</v>
       </c>
       <c r="D97">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="B98">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="C98" t="s">
         <v>36</v>
       </c>
       <c r="D98">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="B99">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="C99" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100">
+        <v>2014</v>
+      </c>
+      <c r="C100" t="s">
+        <v>36</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E100" s="4"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>412</v>
+      </c>
+      <c r="B101">
+        <v>2014</v>
+      </c>
+      <c r="C101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102">
+        <v>2013</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>294</v>
+      </c>
+      <c r="B103">
+        <v>2013</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>302</v>
+      </c>
+      <c r="B104">
+        <v>2013</v>
+      </c>
+      <c r="C104" t="s">
         <v>27</v>
       </c>
-      <c r="D99">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>131</v>
-      </c>
-      <c r="B100">
-        <v>1997</v>
-      </c>
-      <c r="C100" t="s">
-        <v>36</v>
-      </c>
-      <c r="D100">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>199</v>
-      </c>
-      <c r="B101">
-        <v>1998</v>
-      </c>
-      <c r="C101" t="s">
-        <v>36</v>
-      </c>
-      <c r="D101">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>186</v>
-      </c>
-      <c r="B102">
-        <v>1999</v>
-      </c>
-      <c r="C102" t="s">
-        <v>36</v>
-      </c>
-      <c r="D102">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>207</v>
-      </c>
-      <c r="B103">
-        <v>1999</v>
-      </c>
-      <c r="C103" t="s">
-        <v>36</v>
-      </c>
-      <c r="D103">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>154</v>
-      </c>
-      <c r="B104">
-        <v>1999</v>
-      </c>
-      <c r="C104" t="s">
-        <v>36</v>
-      </c>
       <c r="D104">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="B105">
-        <v>2000</v>
+        <v>2013</v>
       </c>
       <c r="C105" t="s">
         <v>36</v>
       </c>
       <c r="D105">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>261</v>
+        <v>145</v>
       </c>
       <c r="B106">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="C106" t="s">
         <v>36</v>
       </c>
       <c r="D106">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>393</v>
       </c>
       <c r="B107">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D107">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>313</v>
+        <v>233</v>
       </c>
       <c r="B108">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="C108" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D108">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="B109">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="C109" t="s">
         <v>36</v>
       </c>
       <c r="D109">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>405</v>
+        <v>99</v>
       </c>
       <c r="B110">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C110" t="s">
         <v>36</v>
       </c>
       <c r="D110">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F110" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="B111">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C111" t="s">
         <v>36</v>
       </c>
-      <c r="D111">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D111" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E111" s="4"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="B112">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C112" t="s">
         <v>36</v>
       </c>
-      <c r="D112">
-        <v>8</v>
-      </c>
+      <c r="D112" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E112" s="4"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>300</v>
+      <c r="A113" t="s">
+        <v>254</v>
       </c>
       <c r="B113">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C113" t="s">
         <v>36</v>
       </c>
-      <c r="D113">
-        <v>8</v>
-      </c>
+      <c r="D113" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E113" s="4"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>299</v>
+        <v>90</v>
       </c>
       <c r="B114">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C114" t="s">
         <v>36</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B115">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C115" t="s">
         <v>36</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="B116">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D116">
-        <v>8</v>
-      </c>
-      <c r="F116" t="s">
-        <v>535</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B117">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="C117" t="s">
         <v>36</v>
       </c>
       <c r="D117">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="B118">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="C118" t="s">
         <v>36</v>
       </c>
       <c r="D118">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B119">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="C119" t="s">
         <v>36</v>
       </c>
       <c r="D119">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="B120">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="C120" t="s">
         <v>36</v>
       </c>
       <c r="D120">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B121">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="C121" t="s">
         <v>36</v>
       </c>
       <c r="D121">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>170</v>
+        <v>363</v>
       </c>
       <c r="B122">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="C122" t="s">
         <v>36</v>
       </c>
-      <c r="D122">
-        <v>8</v>
-      </c>
+      <c r="D122" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E122" s="4"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
@@ -3892,210 +3962,241 @@
         <v>36</v>
       </c>
       <c r="D123">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="B124">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C124" t="s">
         <v>36</v>
       </c>
       <c r="D124">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F124" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="B125">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C125" t="s">
         <v>36</v>
       </c>
       <c r="D125">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
       <c r="B126">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C126" t="s">
         <v>36</v>
       </c>
       <c r="D126">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="B127">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C127" t="s">
         <v>36</v>
       </c>
-      <c r="D127">
-        <v>8</v>
-      </c>
+      <c r="D127" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E127" s="4"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>68</v>
+        <v>400</v>
       </c>
       <c r="B128">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C128" t="s">
         <v>36</v>
       </c>
-      <c r="D128">
-        <v>8</v>
-      </c>
+      <c r="D128" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E128" s="4"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>248</v>
+        <v>37</v>
       </c>
       <c r="B129">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C129" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D129">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>105</v>
+        <v>244</v>
       </c>
       <c r="B130">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C130" t="s">
         <v>36</v>
       </c>
       <c r="D130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F130" t="s">
-        <v>225</v>
+        <v>464</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="B131">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C131" t="s">
         <v>36</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F131" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="B132">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C132" t="s">
         <v>36</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F132" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="B133">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D133">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>459</v>
+        <v>404</v>
+      </c>
+      <c r="B134">
+        <v>2010</v>
       </c>
       <c r="C134" t="s">
         <v>36</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>430</v>
+        <v>250</v>
+      </c>
+      <c r="B135">
+        <v>2010</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>480</v>
+        <v>280</v>
+      </c>
+      <c r="B136">
+        <v>2010</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
-      </c>
-      <c r="D136">
-        <v>8</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E136" s="4"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>413</v>
+        <v>303</v>
+      </c>
+      <c r="B137">
+        <v>2010</v>
       </c>
       <c r="C137" t="s">
         <v>36</v>
       </c>
-      <c r="D137">
-        <v>8</v>
-      </c>
+      <c r="D137" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E137" s="4"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>460</v>
+        <v>102</v>
+      </c>
+      <c r="B138">
+        <v>2009</v>
       </c>
       <c r="C138" t="s">
         <v>36</v>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>418</v>
+        <v>101</v>
+      </c>
+      <c r="B139">
+        <v>2009</v>
       </c>
       <c r="C139" t="s">
         <v>36</v>
@@ -4106,105 +4207,111 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>411</v>
+        <v>76</v>
+      </c>
+      <c r="B140">
+        <v>2009</v>
       </c>
       <c r="C140" t="s">
         <v>36</v>
       </c>
       <c r="D140">
-        <v>8</v>
-      </c>
-      <c r="F140" t="s">
-        <v>456</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>431</v>
+        <v>170</v>
+      </c>
+      <c r="B141">
+        <v>2009</v>
       </c>
       <c r="C141" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D141">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>429</v>
+        <v>166</v>
+      </c>
+      <c r="B142">
+        <v>2009</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="B143">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C143" t="s">
         <v>36</v>
       </c>
       <c r="D143">
-        <v>7.6</v>
+        <v>6</v>
+      </c>
+      <c r="F143" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="B144">
-        <v>1946</v>
+        <v>2009</v>
       </c>
       <c r="C144" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D144">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="B145">
-        <v>1975</v>
+        <v>2009</v>
       </c>
       <c r="C145" t="s">
         <v>36</v>
       </c>
       <c r="D145">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>324</v>
+        <v>41</v>
       </c>
       <c r="B146">
-        <v>1978</v>
+        <v>2008</v>
       </c>
       <c r="C146" t="s">
         <v>36</v>
       </c>
       <c r="D146">
-        <v>7.5</v>
-      </c>
-      <c r="F146" t="s">
-        <v>449</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="B147">
-        <v>1980</v>
+        <v>2008</v>
       </c>
       <c r="C147" t="s">
         <v>36</v>
@@ -4215,167 +4322,175 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>367</v>
+        <v>174</v>
       </c>
       <c r="B148">
-        <v>1984</v>
+        <v>2008</v>
       </c>
       <c r="C148" t="s">
         <v>36</v>
       </c>
       <c r="D148">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="B149">
-        <v>1984</v>
+        <v>2008</v>
       </c>
       <c r="C149" t="s">
         <v>36</v>
       </c>
       <c r="D149">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="B150">
-        <v>1985</v>
+        <v>2008</v>
       </c>
       <c r="C150" t="s">
         <v>36</v>
       </c>
       <c r="D150">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="B151">
-        <v>1986</v>
+        <v>2008</v>
       </c>
       <c r="C151" t="s">
         <v>36</v>
       </c>
       <c r="D151">
-        <v>7.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="F151" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="B152">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="C152" t="s">
         <v>36</v>
       </c>
       <c r="D152">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="B153">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="C153" t="s">
         <v>36</v>
       </c>
-      <c r="D153">
-        <v>7.5</v>
-      </c>
+      <c r="D153" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E153" s="4"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>190</v>
+        <v>391</v>
       </c>
       <c r="B154">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="C154" t="s">
         <v>36</v>
       </c>
-      <c r="D154">
-        <v>7.5</v>
+      <c r="D154" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B155">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="C155" t="s">
         <v>36</v>
       </c>
       <c r="D155">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>377</v>
+        <v>230</v>
       </c>
       <c r="B156">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="C156" t="s">
         <v>36</v>
       </c>
       <c r="D156">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>370</v>
+        <v>275</v>
       </c>
       <c r="B157">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="C157" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D157">
-        <v>7.5</v>
+        <v>8</v>
+      </c>
+      <c r="F157" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="B158">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="C158" t="s">
         <v>36</v>
       </c>
       <c r="D158">
-        <v>7.5</v>
-      </c>
-      <c r="F158" t="s">
-        <v>474</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>293</v>
+        <v>150</v>
       </c>
       <c r="B159">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="C159" t="s">
         <v>36</v>
@@ -4386,27 +4501,24 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>387</v>
+        <v>143</v>
       </c>
       <c r="B160">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="C160" t="s">
         <v>36</v>
       </c>
       <c r="D160">
-        <v>7.5</v>
-      </c>
-      <c r="F160" t="s">
-        <v>482</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="B161">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="C161" t="s">
         <v>36</v>
@@ -4417,10 +4529,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>147</v>
+        <v>406</v>
       </c>
       <c r="B162">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="C162" t="s">
         <v>36</v>
@@ -4428,361 +4540,364 @@
       <c r="D162">
         <v>7.5</v>
       </c>
+      <c r="F162" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>355</v>
+        <v>181</v>
       </c>
       <c r="B163">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D163">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B164">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="C164" t="s">
-        <v>36</v>
-      </c>
-      <c r="D164">
-        <v>7.5</v>
-      </c>
-      <c r="F164" t="s">
-        <v>475</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>130</v>
+        <v>416</v>
       </c>
       <c r="B165">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="C165" t="s">
         <v>36</v>
       </c>
       <c r="D165">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="B166">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="C166" t="s">
         <v>36</v>
       </c>
       <c r="D166">
-        <v>7.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>290</v>
+        <v>26</v>
       </c>
       <c r="B167">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="C167" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D167">
-        <v>7.5</v>
-      </c>
-      <c r="F167" t="s">
-        <v>469</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="B168">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C168" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D168">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="B169">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="C169" t="s">
         <v>36</v>
       </c>
       <c r="D169">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>104</v>
+      <c r="A170" s="2" t="s">
+        <v>553</v>
       </c>
       <c r="B170">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C170" t="s">
         <v>36</v>
       </c>
       <c r="D170">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>242</v>
+        <v>554</v>
       </c>
       <c r="B171">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C171" t="s">
         <v>36</v>
       </c>
       <c r="D171">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>408</v>
+        <v>167</v>
       </c>
       <c r="B172">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C172" t="s">
         <v>36</v>
       </c>
       <c r="D172">
-        <v>7.5</v>
-      </c>
-      <c r="F172" t="s">
-        <v>458</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="B173">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C173" t="s">
         <v>36</v>
       </c>
       <c r="D173">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="B174">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C174" t="s">
         <v>36</v>
       </c>
       <c r="D174">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="B175">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C175" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D175">
-        <v>7.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="F175" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="B176">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C176" t="s">
-        <v>36</v>
-      </c>
-      <c r="D176">
-        <v>7.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E176" s="4"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>140</v>
+        <v>347</v>
       </c>
       <c r="B177">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C177" t="s">
         <v>36</v>
       </c>
-      <c r="D177">
-        <v>7.5</v>
-      </c>
+      <c r="D177" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E177" s="4"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="B178">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C178" t="s">
-        <v>36</v>
-      </c>
-      <c r="D178">
-        <v>7.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E178" s="4"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>341</v>
+        <v>258</v>
       </c>
       <c r="B179">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C179" t="s">
         <v>36</v>
       </c>
-      <c r="D179">
-        <v>7.5</v>
-      </c>
-      <c r="F179" t="s">
-        <v>455</v>
-      </c>
+      <c r="D179" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E179" s="4"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="B180">
-        <v>2022</v>
+        <v>2006</v>
       </c>
       <c r="C180" t="s">
         <v>36</v>
       </c>
-      <c r="D180">
-        <v>7.5</v>
-      </c>
+      <c r="D180" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E180" s="4"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>414</v>
+        <v>155</v>
+      </c>
+      <c r="B181">
+        <v>2005</v>
       </c>
       <c r="C181" t="s">
         <v>36</v>
       </c>
       <c r="D181">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>262</v>
+        <v>63</v>
       </c>
       <c r="B182">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="C182" t="s">
         <v>36</v>
       </c>
       <c r="D182">
-        <v>7.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>171</v>
+        <v>392</v>
       </c>
       <c r="B183">
-        <v>1959</v>
+        <v>2005</v>
       </c>
       <c r="C183" t="s">
         <v>36</v>
       </c>
       <c r="D183">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="B184">
-        <v>1963</v>
+        <v>2005</v>
       </c>
       <c r="C184" t="s">
         <v>36</v>
       </c>
       <c r="D184">
-        <v>7</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F184" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="B185">
-        <v>1971</v>
+        <v>2005</v>
       </c>
       <c r="C185" t="s">
         <v>36</v>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="B186">
-        <v>1972</v>
+        <v>2005</v>
       </c>
       <c r="C186" t="s">
         <v>36</v>
       </c>
       <c r="D186">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="B187">
-        <v>1978</v>
+        <v>2005</v>
       </c>
       <c r="C187" t="s">
         <v>36</v>
@@ -4790,16 +4905,13 @@
       <c r="D187">
         <v>7</v>
       </c>
-      <c r="F187" t="s">
-        <v>450</v>
-      </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="B188">
-        <v>1984</v>
+        <v>2005</v>
       </c>
       <c r="C188" t="s">
         <v>36</v>
@@ -4810,13 +4922,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>315</v>
+        <v>398</v>
       </c>
       <c r="B189">
-        <v>1985</v>
+        <v>2005</v>
       </c>
       <c r="C189" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D189">
         <v>7</v>
@@ -4824,97 +4936,98 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="B190">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="C190" t="s">
-        <v>36</v>
-      </c>
-      <c r="D190">
-        <v>7</v>
-      </c>
-      <c r="F190" t="s">
-        <v>433</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E190" s="4"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="B191">
-        <v>1987</v>
+        <v>2005</v>
       </c>
       <c r="C191" t="s">
         <v>36</v>
       </c>
-      <c r="D191">
-        <v>7</v>
-      </c>
+      <c r="D191" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E191" s="4"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="B192">
-        <v>1988</v>
+        <v>2005</v>
       </c>
       <c r="C192" t="s">
-        <v>36</v>
-      </c>
-      <c r="D192">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E192" s="4"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>371</v>
+        <v>22</v>
       </c>
       <c r="B193">
-        <v>1989</v>
+        <v>2005</v>
       </c>
       <c r="C193" t="s">
-        <v>36</v>
-      </c>
-      <c r="D193">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E193" s="4"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="B194">
-        <v>1989</v>
+        <v>2004</v>
       </c>
       <c r="C194" t="s">
         <v>36</v>
       </c>
       <c r="D194">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>275</v>
+        <v>104</v>
       </c>
       <c r="B195">
-        <v>1991</v>
+        <v>2004</v>
       </c>
       <c r="C195" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D195">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="B196">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="C196" t="s">
         <v>36</v>
@@ -4922,16 +5035,13 @@
       <c r="D196">
         <v>7</v>
       </c>
-      <c r="F196" t="s">
-        <v>473</v>
-      </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>125</v>
+        <v>323</v>
       </c>
       <c r="B197">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="C197" t="s">
         <v>36</v>
@@ -4942,198 +5052,205 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>300</v>
+        <v>117</v>
       </c>
       <c r="B198">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C198" t="s">
         <v>36</v>
       </c>
       <c r="D198">
-        <v>7</v>
-      </c>
-      <c r="F198" t="s">
-        <v>483</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>163</v>
+        <v>433</v>
       </c>
       <c r="B199">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C199" t="s">
         <v>36</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>6.5</v>
+      </c>
+      <c r="F199" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>133</v>
+        <v>399</v>
       </c>
       <c r="B200">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C200" t="s">
         <v>36</v>
       </c>
       <c r="D200">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F200" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>149</v>
+        <v>327</v>
       </c>
       <c r="B201">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C201" t="s">
         <v>36</v>
       </c>
       <c r="D201">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>31</v>
+        <v>301</v>
       </c>
       <c r="B202">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C202" t="s">
-        <v>27</v>
-      </c>
-      <c r="D202">
-        <v>7</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E202" s="4"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="B203">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C203" t="s">
         <v>36</v>
       </c>
-      <c r="D203">
-        <v>7</v>
-      </c>
+      <c r="D203" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E203" s="4"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>180</v>
+        <v>356</v>
       </c>
       <c r="B204">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C204" t="s">
         <v>36</v>
       </c>
-      <c r="D204">
-        <v>7</v>
-      </c>
+      <c r="D204" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E204" s="4"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="B205">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="C205" t="s">
-        <v>27</v>
-      </c>
-      <c r="D205">
-        <v>7</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E205" s="4"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>229</v>
+        <v>386</v>
       </c>
       <c r="B206">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C206" t="s">
         <v>36</v>
       </c>
-      <c r="D206">
-        <v>7</v>
-      </c>
-      <c r="F206" t="s">
-        <v>465</v>
-      </c>
+      <c r="D206" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E206" s="4"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>178</v>
+        <v>330</v>
       </c>
       <c r="B207">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C207" t="s">
         <v>36</v>
       </c>
-      <c r="D207">
-        <v>7</v>
-      </c>
+      <c r="D207" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E207" s="4"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>328</v>
+        <v>210</v>
       </c>
       <c r="B208">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="C208" t="s">
-        <v>27</v>
-      </c>
-      <c r="D208">
-        <v>7</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E208" s="4"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B209">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C209" t="s">
         <v>36</v>
       </c>
       <c r="D209">
-        <v>7</v>
+        <v>9.9</v>
+      </c>
+      <c r="F209" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="B210">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C210" t="s">
         <v>36</v>
       </c>
       <c r="D210">
-        <v>7</v>
-      </c>
-      <c r="F210" t="s">
-        <v>446</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="B211">
         <v>2003</v>
@@ -5142,71 +5259,71 @@
         <v>36</v>
       </c>
       <c r="D211">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="B212">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C212" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D212">
-        <v>7</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B213">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C213" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D213">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>403</v>
+        <v>556</v>
       </c>
       <c r="B214">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C214" t="s">
         <v>36</v>
       </c>
       <c r="D214">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>382</v>
+        <v>209</v>
       </c>
       <c r="B215">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C215" t="s">
         <v>36</v>
       </c>
       <c r="D215">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>400</v>
+        <v>124</v>
       </c>
       <c r="B216">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C216" t="s">
         <v>36</v>
@@ -5217,308 +5334,318 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="B217">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="C217" t="s">
         <v>36</v>
       </c>
-      <c r="D217">
-        <v>7</v>
-      </c>
+      <c r="D217" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E217" s="4"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>181</v>
+        <v>395</v>
       </c>
       <c r="B218">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C218" t="s">
         <v>36</v>
       </c>
-      <c r="D218">
-        <v>7</v>
-      </c>
+      <c r="D218" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E218" s="4"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="B219">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C219" t="s">
         <v>36</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>383</v>
+        <v>55</v>
       </c>
       <c r="B220">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C220" t="s">
         <v>36</v>
       </c>
       <c r="D220">
-        <v>7</v>
+        <v>9.9</v>
+      </c>
+      <c r="F220" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="B221">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C221" t="s">
         <v>36</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>166</v>
+        <v>436</v>
       </c>
       <c r="B222">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="C222" t="s">
         <v>36</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="F222" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>245</v>
+        <v>480</v>
       </c>
       <c r="B223">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C223" t="s">
         <v>36</v>
       </c>
       <c r="D223">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F223" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="B224">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C224" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D224">
-        <v>7</v>
-      </c>
-      <c r="F224" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B225">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C225" t="s">
         <v>36</v>
       </c>
       <c r="D225">
-        <v>7</v>
-      </c>
-      <c r="F225" t="s">
-        <v>470</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>352</v>
+        <v>211</v>
       </c>
       <c r="B226">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C226" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D226">
         <v>7</v>
       </c>
+      <c r="F226" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>348</v>
+        <v>197</v>
       </c>
       <c r="B227">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C227" t="s">
         <v>36</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F227" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="B228">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C228" t="s">
         <v>36</v>
       </c>
-      <c r="D228">
-        <v>7</v>
-      </c>
+      <c r="D228" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E228" s="4"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="B229">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C229" t="s">
-        <v>36</v>
-      </c>
-      <c r="D229">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E229" s="4"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>122</v>
+        <v>284</v>
       </c>
       <c r="B230">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C230" t="s">
         <v>36</v>
       </c>
-      <c r="D230">
-        <v>7</v>
-      </c>
+      <c r="D230" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E230" s="4"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>288</v>
+        <v>362</v>
       </c>
       <c r="B231">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="C231" t="s">
         <v>36</v>
       </c>
-      <c r="D231">
-        <v>7</v>
-      </c>
+      <c r="D231" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E231" s="4"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>295</v>
+        <v>213</v>
       </c>
       <c r="B232">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="C232" t="s">
         <v>36</v>
       </c>
-      <c r="D232">
-        <v>7</v>
-      </c>
+      <c r="D232" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E232" s="4"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>304</v>
+        <v>49</v>
       </c>
       <c r="B233">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="C233" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D233">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>66</v>
+        <v>260</v>
       </c>
       <c r="B234">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C234" t="s">
         <v>36</v>
       </c>
       <c r="D234">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="B235">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C235" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D235">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="B236">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C236" t="s">
         <v>36</v>
       </c>
       <c r="D236">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F236" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="B237">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C237" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D237">
         <v>7</v>
@@ -5526,10 +5653,10 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="B238">
-        <v>2015</v>
+        <v>2001</v>
       </c>
       <c r="C238" t="s">
         <v>36</v>
@@ -5537,47 +5664,45 @@
       <c r="D238">
         <v>7</v>
       </c>
-      <c r="F238" t="s">
-        <v>440</v>
-      </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="B239">
-        <v>2015</v>
+        <v>2001</v>
       </c>
       <c r="C239" t="s">
         <v>36</v>
       </c>
       <c r="D239">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="B240">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="C240" t="s">
-        <v>36</v>
-      </c>
-      <c r="D240">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E240" s="4"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>121</v>
+        <v>476</v>
       </c>
       <c r="B241">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="C241" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D241">
         <v>7</v>
@@ -5585,80 +5710,83 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>112</v>
+        <v>457</v>
       </c>
       <c r="B242">
-        <v>2018</v>
+        <v>2001</v>
       </c>
       <c r="C242" t="s">
         <v>36</v>
       </c>
       <c r="D242">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="B243">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="C243" t="s">
         <v>36</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="B244">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="C244" t="s">
         <v>36</v>
       </c>
       <c r="D244">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>336</v>
+        <v>135</v>
       </c>
       <c r="B245">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="C245" t="s">
         <v>36</v>
       </c>
       <c r="D245">
-        <v>7</v>
+        <v>7.5</v>
+      </c>
+      <c r="F245" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B246">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="C246" t="s">
         <v>36</v>
       </c>
       <c r="D246">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B247">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="C247" t="s">
         <v>36</v>
@@ -5666,13 +5794,16 @@
       <c r="D247">
         <v>7</v>
       </c>
+      <c r="F247" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="B248">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="C248" t="s">
         <v>36</v>
@@ -5680,80 +5811,85 @@
       <c r="D248">
         <v>7</v>
       </c>
-      <c r="F248" t="s">
-        <v>468</v>
-      </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="B249">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="C249" t="s">
         <v>36</v>
       </c>
-      <c r="D249">
-        <v>7</v>
-      </c>
+      <c r="D249" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E249" s="4"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B250">
-        <v>2023</v>
+        <v>2000</v>
       </c>
       <c r="C250" t="s">
         <v>36</v>
       </c>
-      <c r="D250">
-        <v>7</v>
-      </c>
+      <c r="D250" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E250" s="4"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B251">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="C251" t="s">
         <v>36</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>432</v>
+        <v>53</v>
+      </c>
+      <c r="B252">
+        <v>1999</v>
       </c>
       <c r="C252" t="s">
         <v>36</v>
       </c>
       <c r="D252">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>480</v>
+        <v>40</v>
+      </c>
+      <c r="B253">
+        <v>1999</v>
       </c>
       <c r="C253" t="s">
         <v>36</v>
       </c>
       <c r="D253">
-        <v>7</v>
-      </c>
-      <c r="F253" t="s">
-        <v>469</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>415</v>
+        <v>186</v>
+      </c>
+      <c r="B254">
+        <v>1999</v>
       </c>
       <c r="C254" t="s">
         <v>36</v>
@@ -5764,66 +5900,69 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>546</v>
+        <v>206</v>
+      </c>
+      <c r="B255">
+        <v>1999</v>
       </c>
       <c r="C255" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>542</v>
+        <v>154</v>
       </c>
       <c r="B256">
-        <v>1977</v>
+        <v>1999</v>
       </c>
       <c r="C256" t="s">
         <v>36</v>
       </c>
       <c r="D256">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>273</v>
+        <v>353</v>
       </c>
       <c r="B257">
-        <v>1988</v>
+        <v>1999</v>
       </c>
       <c r="C257" t="s">
         <v>27</v>
       </c>
       <c r="D257">
-        <v>6.5</v>
+        <v>7</v>
+      </c>
+      <c r="F257" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>268</v>
+        <v>30</v>
       </c>
       <c r="B258">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="C258" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D258">
-        <v>6.5</v>
-      </c>
-      <c r="F258" t="s">
-        <v>454</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>376</v>
+        <v>291</v>
       </c>
       <c r="B259">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C259" t="s">
         <v>36</v>
@@ -5831,13 +5970,10 @@
       <c r="D259">
         <v>6.5</v>
       </c>
-      <c r="F259" t="s">
-        <v>417</v>
-      </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="B260">
         <v>1999</v>
@@ -5845,238 +5981,227 @@
       <c r="C260" t="s">
         <v>36</v>
       </c>
-      <c r="D260">
-        <v>6.5</v>
-      </c>
+      <c r="D260" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E260" s="4"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>185</v>
+        <v>427</v>
       </c>
       <c r="B261">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C261" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D261">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>117</v>
+        <v>305</v>
       </c>
       <c r="B262">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C262" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D262">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>435</v>
+        <v>198</v>
       </c>
       <c r="B263">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C263" t="s">
         <v>36</v>
       </c>
       <c r="D263">
-        <v>6.5</v>
-      </c>
-      <c r="F263" t="s">
-        <v>434</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>345</v>
+        <v>94</v>
       </c>
       <c r="B264">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="C264" t="s">
         <v>36</v>
       </c>
       <c r="D264">
-        <v>6.5</v>
-      </c>
-      <c r="F264" t="s">
-        <v>462</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="B265">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="C265" t="s">
         <v>36</v>
       </c>
       <c r="D265">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>67</v>
+        <v>261</v>
       </c>
       <c r="B266">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C266" t="s">
         <v>36</v>
       </c>
       <c r="D266">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B267">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C267" t="s">
         <v>36</v>
       </c>
       <c r="D267">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="B268">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C268" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D268">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B269">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="C269" t="s">
         <v>36</v>
       </c>
       <c r="D269">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>399</v>
+        <v>180</v>
       </c>
       <c r="B270">
-        <v>2016</v>
+        <v>1998</v>
       </c>
       <c r="C270" t="s">
         <v>36</v>
       </c>
       <c r="D270">
-        <v>6.5</v>
-      </c>
-      <c r="F270" t="s">
-        <v>434</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B271">
-        <v>2016</v>
+        <v>1998</v>
       </c>
       <c r="C271" t="s">
         <v>36</v>
       </c>
       <c r="D271">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>321</v>
+        <v>430</v>
       </c>
       <c r="B272">
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="C272" t="s">
         <v>36</v>
       </c>
       <c r="D272">
-        <v>6.5</v>
-      </c>
-      <c r="F272" t="s">
-        <v>479</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>351</v>
+        <v>212</v>
       </c>
       <c r="B273">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="C273" t="s">
         <v>36</v>
       </c>
       <c r="D273">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="B274">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="C274" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D274">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>269</v>
+        <v>131</v>
       </c>
       <c r="B275">
-        <v>2022</v>
+        <v>1997</v>
       </c>
       <c r="C275" t="s">
         <v>36</v>
       </c>
       <c r="D275">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>246</v>
+        <v>385</v>
       </c>
       <c r="B276">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="C276" t="s">
         <v>36</v>
@@ -6084,53 +6209,53 @@
       <c r="D276">
         <v>6.5</v>
       </c>
+      <c r="F276" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>443</v>
+        <v>163</v>
       </c>
       <c r="B277">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="C277" t="s">
         <v>36</v>
       </c>
       <c r="D277">
-        <v>6.5</v>
-      </c>
-      <c r="F277" t="s">
-        <v>442</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>477</v>
+        <v>133</v>
+      </c>
+      <c r="B278">
+        <v>1997</v>
       </c>
       <c r="C278" t="s">
         <v>36</v>
       </c>
       <c r="D278">
-        <v>6.5</v>
-      </c>
-      <c r="F278" t="s">
-        <v>478</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>195</v>
+        <v>374</v>
       </c>
       <c r="B279">
-        <v>1965</v>
+        <v>1997</v>
       </c>
       <c r="C279" t="s">
         <v>36</v>
       </c>
       <c r="D279">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F279" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -6149,538 +6274,536 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>205</v>
+        <v>379</v>
       </c>
       <c r="B281">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C281" t="s">
         <v>36</v>
       </c>
-      <c r="D281">
-        <v>6</v>
-      </c>
+      <c r="D281" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E281" s="4"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="B282">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="C282" t="s">
-        <v>36</v>
-      </c>
-      <c r="D282">
-        <v>6</v>
-      </c>
-      <c r="F282" t="s">
-        <v>481</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E282" s="4"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="B283">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C283" t="s">
         <v>36</v>
       </c>
-      <c r="D283">
-        <v>6</v>
-      </c>
-      <c r="F283" t="s">
-        <v>464</v>
-      </c>
+      <c r="D283" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E283" s="4"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>286</v>
+        <v>429</v>
       </c>
       <c r="B284">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="C284" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D284">
-        <v>6</v>
-      </c>
-      <c r="F284" t="s">
-        <v>466</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B285">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="C285" t="s">
         <v>36</v>
       </c>
       <c r="D285">
-        <v>6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="B286">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="C286" t="s">
         <v>36</v>
       </c>
       <c r="D286">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B287">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="C287" t="s">
         <v>36</v>
       </c>
       <c r="D287">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>173</v>
+        <v>292</v>
       </c>
       <c r="B288">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="C288" t="s">
         <v>36</v>
       </c>
       <c r="D288">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="B289">
-        <v>2013</v>
+        <v>1996</v>
       </c>
       <c r="C289" t="s">
         <v>36</v>
       </c>
       <c r="D289">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F289" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="B290">
-        <v>2014</v>
+        <v>1996</v>
       </c>
       <c r="C290" t="s">
         <v>36</v>
       </c>
-      <c r="D290">
-        <v>6</v>
-      </c>
+      <c r="D290" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E290" s="4"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
       <c r="B291">
-        <v>2014</v>
+        <v>1996</v>
       </c>
       <c r="C291" t="s">
         <v>36</v>
       </c>
-      <c r="D291">
-        <v>6</v>
-      </c>
+      <c r="D291" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E291" s="4"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B292">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="C292" t="s">
         <v>36</v>
       </c>
-      <c r="D292">
-        <v>6</v>
-      </c>
+      <c r="D292" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E292" s="4"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="B293">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="C293" t="s">
         <v>36</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B294">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C294" t="s">
         <v>36</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="B295">
-        <v>2017</v>
+        <v>1995</v>
       </c>
       <c r="C295" t="s">
         <v>36</v>
       </c>
       <c r="D295">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="B296">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="C296" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D296">
-        <v>6</v>
-      </c>
-      <c r="F296" t="s">
-        <v>441</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>354</v>
+        <v>164</v>
       </c>
       <c r="B297">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="C297" t="s">
         <v>36</v>
       </c>
       <c r="D297">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B298">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="C298" t="s">
         <v>36</v>
       </c>
       <c r="D298">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F298" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>512</v>
+        <v>125</v>
       </c>
       <c r="B299">
-        <v>2022</v>
+        <v>1995</v>
       </c>
       <c r="C299" t="s">
         <v>36</v>
       </c>
       <c r="D299">
-        <v>6</v>
-      </c>
-      <c r="F299" t="s">
-        <v>513</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>510</v>
+        <v>255</v>
       </c>
       <c r="B300">
-        <v>2024</v>
+        <v>1995</v>
       </c>
       <c r="C300" t="s">
         <v>36</v>
       </c>
-      <c r="D300">
-        <v>6</v>
-      </c>
-      <c r="F300" t="s">
-        <v>511</v>
-      </c>
+      <c r="D300" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E300" s="4"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B301">
-        <v>2024</v>
+        <v>1995</v>
       </c>
       <c r="C301" t="s">
         <v>27</v>
       </c>
       <c r="D301">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="B302">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="C302" t="s">
         <v>36</v>
       </c>
       <c r="D302">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B303">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="C303" t="s">
         <v>36</v>
       </c>
       <c r="D303">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>420</v>
+        <v>91</v>
+      </c>
+      <c r="B304">
+        <v>1994</v>
       </c>
       <c r="C304" t="s">
         <v>36</v>
       </c>
       <c r="D304">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B305">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="C305" t="s">
         <v>36</v>
       </c>
       <c r="D305">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>406</v>
+        <v>295</v>
       </c>
       <c r="B306">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="C306" t="s">
         <v>36</v>
       </c>
-      <c r="D306">
-        <v>5</v>
-      </c>
+      <c r="D306" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E306" s="4"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="B307">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="C307" t="s">
-        <v>36</v>
-      </c>
-      <c r="D307">
         <v>5</v>
       </c>
+      <c r="D307" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E307" s="4"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="B308">
-        <v>2012</v>
+        <v>1994</v>
       </c>
       <c r="C308" t="s">
         <v>36</v>
       </c>
       <c r="D308">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B309">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="C309" t="s">
         <v>36</v>
       </c>
       <c r="D309">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>182</v>
+        <v>306</v>
       </c>
       <c r="B310">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="C310" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D310">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B311">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C311" t="s">
         <v>36</v>
       </c>
       <c r="D311">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>177</v>
+        <v>331</v>
       </c>
       <c r="B312">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C312" t="s">
         <v>36</v>
       </c>
       <c r="D312">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F312" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B313">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="C313" t="s">
         <v>36</v>
       </c>
-      <c r="D313">
-        <v>5</v>
-      </c>
+      <c r="D313" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E313" s="4"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>436</v>
+        <v>357</v>
       </c>
       <c r="B314">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C314" t="s">
         <v>36</v>
       </c>
-      <c r="D314">
-        <v>5</v>
-      </c>
-      <c r="F314" t="s">
-        <v>434</v>
-      </c>
+      <c r="D314" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E314" s="4"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>437</v>
+        <v>262</v>
       </c>
       <c r="B315">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C315" t="s">
         <v>36</v>
       </c>
-      <c r="D315">
-        <v>5</v>
-      </c>
-      <c r="F315" t="s">
-        <v>434</v>
-      </c>
+      <c r="D315" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E315" s="4"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>412</v>
+        <v>355</v>
       </c>
       <c r="B316">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C316" t="s">
-        <v>36</v>
-      </c>
-      <c r="D316">
         <v>5</v>
       </c>
-      <c r="F316" t="s">
-        <v>486</v>
-      </c>
+      <c r="D316" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E316" s="4"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>416</v>
+        <v>414</v>
+      </c>
+      <c r="B317">
+        <v>1993</v>
       </c>
       <c r="C317" t="s">
         <v>36</v>
@@ -6691,652 +6814,609 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>312</v>
+        <v>127</v>
       </c>
       <c r="B318">
-        <v>2006</v>
+        <v>1992</v>
       </c>
       <c r="C318" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D318">
-        <v>4.5</v>
-      </c>
-      <c r="F318" t="s">
-        <v>410</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="B319">
-        <v>2008</v>
+        <v>1992</v>
       </c>
       <c r="C319" t="s">
         <v>36</v>
       </c>
       <c r="D319">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="B320">
-        <v>2018</v>
+        <v>1992</v>
       </c>
       <c r="C320" t="s">
         <v>36</v>
       </c>
-      <c r="D320">
-        <v>4.5</v>
-      </c>
-      <c r="F320" t="s">
-        <v>427</v>
-      </c>
+      <c r="D320" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E320" s="4"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="B321">
-        <v>2024</v>
+        <v>1992</v>
       </c>
       <c r="C321" t="s">
-        <v>36</v>
-      </c>
-      <c r="D321">
-        <v>4.5</v>
-      </c>
-      <c r="F321" t="s">
-        <v>426</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E321" s="4"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="B322">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="C322" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D322">
-        <v>4.5</v>
-      </c>
-      <c r="F322" t="s">
-        <v>428</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="B323">
-        <v>2016</v>
+        <v>1991</v>
       </c>
       <c r="C323" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D323">
-        <v>4</v>
-      </c>
-      <c r="F323" t="s">
-        <v>424</v>
+        <v>9</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>132</v>
+        <v>318</v>
       </c>
       <c r="B324">
-        <v>2017</v>
+        <v>1991</v>
       </c>
       <c r="C324" t="s">
         <v>36</v>
       </c>
       <c r="D324">
-        <v>4</v>
-      </c>
-      <c r="F324" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="B325">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="C325" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D325">
-        <v>4</v>
-      </c>
-      <c r="F325" t="s">
-        <v>422</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>444</v>
+        <v>274</v>
       </c>
       <c r="B326">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="C326" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D326">
-        <v>3.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>329</v>
+        <v>196</v>
       </c>
       <c r="B327">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="C327" t="s">
         <v>36</v>
       </c>
       <c r="D327">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B328">
-        <v>2013</v>
+        <v>1990</v>
       </c>
       <c r="C328" t="s">
         <v>36</v>
       </c>
       <c r="D328">
-        <v>3</v>
-      </c>
-      <c r="F328" t="s">
-        <v>425</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>184</v>
+        <v>341</v>
       </c>
       <c r="B329">
-        <v>2017</v>
+        <v>1990</v>
       </c>
       <c r="C329" t="s">
         <v>36</v>
       </c>
       <c r="D329">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F329" t="s">
-        <v>514</v>
+        <v>450</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>266</v>
+        <v>59</v>
       </c>
       <c r="B330">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="C330" t="s">
-        <v>5</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E330" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D330">
+        <v>8</v>
+      </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>289</v>
+        <v>372</v>
       </c>
       <c r="B331">
-        <v>1951</v>
+        <v>1990</v>
       </c>
       <c r="C331" t="s">
-        <v>5</v>
-      </c>
-      <c r="D331" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E331" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D331">
+        <v>8</v>
+      </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>15</v>
+        <v>338</v>
       </c>
       <c r="B332">
-        <v>1954</v>
+        <v>1990</v>
       </c>
       <c r="C332" t="s">
-        <v>5</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E332" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D332">
+        <v>8</v>
+      </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="B333">
-        <v>1954</v>
+        <v>1990</v>
       </c>
       <c r="C333" t="s">
-        <v>5</v>
-      </c>
-      <c r="D333" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E333" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D333">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>4</v>
+        <v>375</v>
       </c>
       <c r="B334">
-        <v>1957</v>
+        <v>1990</v>
       </c>
       <c r="C334" t="s">
-        <v>5</v>
-      </c>
-      <c r="D334" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E334" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D334">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>19</v>
+        <v>267</v>
       </c>
       <c r="B335">
-        <v>1963</v>
+        <v>1990</v>
       </c>
       <c r="C335" t="s">
-        <v>5</v>
-      </c>
-      <c r="D335" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E335" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D335">
+        <v>6.5</v>
+      </c>
+      <c r="F335" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>6</v>
+        <v>387</v>
       </c>
       <c r="B336">
-        <v>1968</v>
+        <v>1990</v>
       </c>
       <c r="C336" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E336" s="4"/>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>282</v>
+        <v>89</v>
       </c>
       <c r="B337">
-        <v>1968</v>
+        <v>1989</v>
       </c>
       <c r="C337" t="s">
         <v>36</v>
       </c>
-      <c r="D337" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E337" s="4"/>
+      <c r="D337">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>392</v>
+        <v>169</v>
       </c>
       <c r="B338">
-        <v>1968</v>
+        <v>1989</v>
       </c>
       <c r="C338" t="s">
-        <v>5</v>
-      </c>
-      <c r="D338" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E338" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D338">
+        <v>9</v>
+      </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="B339">
-        <v>1973</v>
+        <v>1989</v>
       </c>
       <c r="C339" t="s">
-        <v>5</v>
-      </c>
-      <c r="D339" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E339" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D339">
+        <v>8</v>
+      </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B340">
-        <v>1973</v>
+        <v>1989</v>
       </c>
       <c r="C340" t="s">
         <v>36</v>
       </c>
-      <c r="D340" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E340" s="4"/>
+      <c r="D340">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>243</v>
+        <v>369</v>
       </c>
       <c r="B341">
-        <v>1973</v>
+        <v>1989</v>
       </c>
       <c r="C341" t="s">
         <v>36</v>
       </c>
-      <c r="D341" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E341" s="4"/>
+      <c r="D341">
+        <v>7</v>
+      </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B342">
-        <v>1976</v>
+        <v>1989</v>
       </c>
       <c r="C342" t="s">
         <v>36</v>
       </c>
-      <c r="D342" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E342" s="4"/>
+      <c r="D342">
+        <v>7</v>
+      </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>13</v>
+        <v>364</v>
       </c>
       <c r="B343">
-        <v>1977</v>
+        <v>1989</v>
       </c>
       <c r="C343" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E343" s="4"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="B344">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="C344" t="s">
         <v>36</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E344" s="4"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>362</v>
+        <v>538</v>
       </c>
       <c r="B345">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="C345" t="s">
         <v>36</v>
       </c>
-      <c r="D345" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E345" s="4"/>
+      <c r="D345">
+        <v>9</v>
+      </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="B346">
-        <v>1981</v>
+        <v>1988</v>
       </c>
       <c r="C346" t="s">
         <v>36</v>
       </c>
-      <c r="D346" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E346" s="4"/>
+      <c r="D346">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>346</v>
+        <v>229</v>
       </c>
       <c r="B347">
-        <v>1981</v>
+        <v>1988</v>
       </c>
       <c r="C347" t="s">
         <v>36</v>
       </c>
-      <c r="D347" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E347" s="4"/>
+      <c r="D347">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="B348">
-        <v>1981</v>
+        <v>1988</v>
       </c>
       <c r="C348" t="s">
         <v>36</v>
       </c>
-      <c r="D348" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E348" s="4"/>
+      <c r="D348">
+        <v>7</v>
+      </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="B349">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="C349" t="s">
-        <v>5</v>
-      </c>
-      <c r="D349" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E349" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D349">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>369</v>
+        <v>23</v>
       </c>
       <c r="B350">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="C350" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E350" s="4"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>361</v>
+        <v>535</v>
       </c>
       <c r="B351">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="C351" t="s">
         <v>36</v>
       </c>
-      <c r="D351" s="4" t="s">
-        <v>548</v>
+      <c r="D351" s="4">
+        <v>7</v>
       </c>
       <c r="E351" s="4"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B352">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="C352" t="s">
-        <v>5</v>
-      </c>
-      <c r="D352" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E352" s="4"/>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D352">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>385</v>
+        <v>214</v>
       </c>
       <c r="B353">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C353" t="s">
         <v>36</v>
       </c>
-      <c r="D353" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E353" s="4"/>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D353">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>277</v>
+        <v>161</v>
       </c>
       <c r="B354">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C354" t="s">
         <v>36</v>
       </c>
-      <c r="D354" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E354" s="4"/>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D354">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>17</v>
+        <v>370</v>
       </c>
       <c r="B355">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C355" t="s">
-        <v>5</v>
-      </c>
-      <c r="D355" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E355" s="4"/>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D355">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>368</v>
+        <v>152</v>
       </c>
       <c r="B356">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="C356" t="s">
         <v>36</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E356" s="4"/>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B357">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C357" t="s">
-        <v>5</v>
-      </c>
-      <c r="D357" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E357" s="4"/>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D357">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B358">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C358" t="s">
-        <v>5</v>
-      </c>
-      <c r="D358" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E358" s="4"/>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D358">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>136</v>
+        <v>384</v>
       </c>
       <c r="B359">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C359" t="s">
         <v>36</v>
       </c>
-      <c r="D359" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E359" s="4"/>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D359">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>297</v>
+        <v>377</v>
       </c>
       <c r="B360">
         <v>1986</v>
@@ -7344,29 +7424,31 @@
       <c r="C360" t="s">
         <v>36</v>
       </c>
-      <c r="D360" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E360" s="4"/>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D360">
+        <v>7</v>
+      </c>
+      <c r="F360" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="B361">
         <v>1986</v>
       </c>
       <c r="C361" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E361" s="4"/>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="B362">
         <v>1986</v>
@@ -7375,1173 +7457,1114 @@
         <v>5</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E362" s="4"/>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="B363">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C363" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E363" s="4"/>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>23</v>
+        <v>534</v>
       </c>
       <c r="B364">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="C364" t="s">
+        <v>36</v>
+      </c>
+      <c r="D364" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="E364" s="4"/>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>48</v>
+      </c>
+      <c r="B365">
+        <v>1985</v>
+      </c>
+      <c r="C365" t="s">
+        <v>36</v>
+      </c>
+      <c r="D365">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>256</v>
+      </c>
+      <c r="B366">
+        <v>1985</v>
+      </c>
+      <c r="C366" t="s">
+        <v>36</v>
+      </c>
+      <c r="D366">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>313</v>
+      </c>
+      <c r="B367">
+        <v>1985</v>
+      </c>
+      <c r="C367" t="s">
+        <v>27</v>
+      </c>
+      <c r="D367">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>24</v>
+      </c>
+      <c r="B368">
+        <v>1985</v>
+      </c>
+      <c r="C368" t="s">
         <v>5</v>
       </c>
-      <c r="D364" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E364" s="4"/>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>366</v>
-      </c>
-      <c r="B365">
-        <v>1989</v>
-      </c>
-      <c r="C365" t="s">
-        <v>36</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E365" s="4"/>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>118</v>
-      </c>
-      <c r="B366">
-        <v>1989</v>
-      </c>
-      <c r="C366" t="s">
-        <v>36</v>
-      </c>
-      <c r="D366" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E366" s="4"/>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>389</v>
-      </c>
-      <c r="B367">
-        <v>1990</v>
-      </c>
-      <c r="C367" t="s">
-        <v>36</v>
-      </c>
-      <c r="D367" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E367" s="4"/>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>404</v>
-      </c>
-      <c r="B368">
-        <v>1992</v>
-      </c>
-      <c r="C368" t="s">
-        <v>36</v>
-      </c>
       <c r="D368" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E368" s="4"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="B369">
-        <v>1992</v>
+        <v>1985</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E369" s="4"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="B370">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="C370" t="s">
         <v>36</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E370" s="4"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B371">
-        <v>1993</v>
+        <v>1984</v>
       </c>
       <c r="C371" t="s">
         <v>36</v>
       </c>
-      <c r="D371" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E371" s="4"/>
+      <c r="D371">
+        <v>9</v>
+      </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>263</v>
+        <v>61</v>
       </c>
       <c r="B372">
-        <v>1993</v>
+        <v>1984</v>
       </c>
       <c r="C372" t="s">
         <v>36</v>
       </c>
-      <c r="D372" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E372" s="4"/>
+      <c r="D372">
+        <v>9</v>
+      </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B373">
-        <v>1993</v>
+        <v>1984</v>
       </c>
       <c r="C373" t="s">
-        <v>5</v>
-      </c>
-      <c r="D373" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E373" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D373">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="B374">
-        <v>1994</v>
+        <v>1984</v>
       </c>
       <c r="C374" t="s">
         <v>36</v>
       </c>
-      <c r="D374" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E374" s="4"/>
+      <c r="D374">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="B375">
-        <v>1994</v>
+        <v>1984</v>
       </c>
       <c r="C375" t="s">
-        <v>5</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E375" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D375">
+        <v>7</v>
+      </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>256</v>
+        <v>366</v>
       </c>
       <c r="B376">
-        <v>1995</v>
+        <v>1984</v>
       </c>
       <c r="C376" t="s">
         <v>36</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E376" s="4"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>298</v>
+        <v>128</v>
       </c>
       <c r="B377">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="C377" t="s">
         <v>36</v>
       </c>
-      <c r="D377" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E377" s="4"/>
+      <c r="D377">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>334</v>
+        <v>383</v>
       </c>
       <c r="B378">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="C378" t="s">
         <v>36</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E378" s="4"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B379">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="C379" t="s">
         <v>36</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E379" s="4"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>381</v>
+        <v>17</v>
       </c>
       <c r="B380">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="C380" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E380" s="4"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B381">
-        <v>1997</v>
+        <v>1982</v>
       </c>
       <c r="C381" t="s">
-        <v>5</v>
-      </c>
-      <c r="D381" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E381" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D381">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>331</v>
+        <v>57</v>
       </c>
       <c r="B382">
-        <v>1997</v>
+        <v>1982</v>
       </c>
       <c r="C382" t="s">
         <v>36</v>
       </c>
-      <c r="D382" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E382" s="4"/>
+      <c r="D382">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>327</v>
+        <v>188</v>
       </c>
       <c r="B383">
-        <v>1999</v>
+        <v>1982</v>
       </c>
       <c r="C383" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E383" s="4"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B384">
-        <v>2000</v>
+        <v>1982</v>
       </c>
       <c r="C384" t="s">
         <v>36</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E384" s="4"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>111</v>
+        <v>359</v>
       </c>
       <c r="B385">
-        <v>2000</v>
+        <v>1982</v>
       </c>
       <c r="C385" t="s">
         <v>36</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E385" s="4"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B386">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E386" s="4"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>209</v>
+        <v>536</v>
       </c>
       <c r="B387">
-        <v>2002</v>
+        <v>1982</v>
       </c>
       <c r="C387" t="s">
         <v>36</v>
       </c>
-      <c r="D387" s="4" t="s">
-        <v>548</v>
+      <c r="D387" s="4">
+        <v>7.5</v>
       </c>
       <c r="E387" s="4"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="B388">
-        <v>2002</v>
+        <v>1981</v>
       </c>
       <c r="C388" t="s">
-        <v>5</v>
-      </c>
-      <c r="D388" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E388" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D388">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>285</v>
+        <v>159</v>
       </c>
       <c r="B389">
-        <v>2002</v>
+        <v>1981</v>
       </c>
       <c r="C389" t="s">
         <v>36</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E389" s="4"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B390">
-        <v>2002</v>
+        <v>1981</v>
       </c>
       <c r="C390" t="s">
         <v>36</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E390" s="4"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="B391">
-        <v>2002</v>
+        <v>1981</v>
       </c>
       <c r="C391" t="s">
         <v>36</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E391" s="4"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>302</v>
+        <v>225</v>
       </c>
       <c r="B392">
-        <v>2003</v>
+        <v>1980</v>
       </c>
       <c r="C392" t="s">
         <v>36</v>
       </c>
-      <c r="D392" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E392" s="4"/>
+      <c r="D392">
+        <v>10</v>
+      </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>397</v>
+        <v>103</v>
       </c>
       <c r="B393">
-        <v>2003</v>
+        <v>1980</v>
       </c>
       <c r="C393" t="s">
         <v>36</v>
       </c>
-      <c r="D393" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E393" s="4"/>
+      <c r="D393">
+        <v>9</v>
+      </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>303</v>
+        <v>172</v>
       </c>
       <c r="B394">
-        <v>2004</v>
+        <v>1980</v>
       </c>
       <c r="C394" t="s">
         <v>36</v>
       </c>
-      <c r="D394" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E394" s="4"/>
+      <c r="D394">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>283</v>
+        <v>46</v>
       </c>
       <c r="B395">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C395" t="s">
         <v>36</v>
       </c>
-      <c r="D395" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E395" s="4"/>
+      <c r="D395">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>358</v>
+        <v>108</v>
       </c>
       <c r="B396">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C396" t="s">
         <v>36</v>
       </c>
-      <c r="D396" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E396" s="4"/>
+      <c r="D396">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>157</v>
+        <v>443</v>
       </c>
       <c r="B397">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C397" t="s">
         <v>36</v>
       </c>
-      <c r="D397" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E397" s="4"/>
+      <c r="D397">
+        <v>8</v>
+      </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>388</v>
+        <v>199</v>
       </c>
       <c r="B398">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C398" t="s">
         <v>36</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E398" s="4"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="B399">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C399" t="s">
         <v>36</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E399" s="4"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>211</v>
+        <v>541</v>
       </c>
       <c r="B400">
-        <v>2004</v>
+        <v>1979</v>
       </c>
       <c r="C400" t="s">
-        <v>36</v>
-      </c>
-      <c r="D400" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E400" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D400">
+        <v>7</v>
+      </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B401">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="C401" t="s">
-        <v>5</v>
-      </c>
-      <c r="D401" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E401" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D401">
+        <v>7.5</v>
+      </c>
+      <c r="F401" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>398</v>
+        <v>345</v>
       </c>
       <c r="B402">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="C402" t="s">
         <v>36</v>
       </c>
-      <c r="D402" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E402" s="4"/>
+      <c r="D402">
+        <v>7</v>
+      </c>
+      <c r="F402" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>237</v>
+        <v>409</v>
       </c>
       <c r="B403">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="C403" t="s">
-        <v>5</v>
-      </c>
-      <c r="D403" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E403" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D403">
+        <v>8</v>
+      </c>
+      <c r="F403" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B404">
-        <v>2005</v>
+        <v>1977</v>
       </c>
       <c r="C404" t="s">
-        <v>5</v>
-      </c>
-      <c r="D404" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E404" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D404">
+        <v>9</v>
+      </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>21</v>
+        <v>537</v>
       </c>
       <c r="B405">
-        <v>2006</v>
+        <v>1977</v>
       </c>
       <c r="C405" t="s">
-        <v>5</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E405" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D405">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>349</v>
+        <v>13</v>
       </c>
       <c r="B406">
-        <v>2006</v>
+        <v>1977</v>
       </c>
       <c r="C406" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E406" s="4"/>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>14</v>
+        <v>361</v>
       </c>
       <c r="B407">
-        <v>2006</v>
+        <v>1976</v>
       </c>
       <c r="C407" t="s">
-        <v>5</v>
-      </c>
-      <c r="D407" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E407" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D407">
+        <v>8</v>
+      </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="B408">
-        <v>2006</v>
+        <v>1976</v>
       </c>
       <c r="C408" t="s">
         <v>36</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E408" s="4"/>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>309</v>
+        <v>168</v>
       </c>
       <c r="B409">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="C409" t="s">
         <v>36</v>
       </c>
-      <c r="D409" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E409" s="4"/>
+      <c r="D409">
+        <v>9</v>
+      </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="B410">
-        <v>2007</v>
+        <v>1975</v>
       </c>
       <c r="C410" t="s">
-        <v>5</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E410" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D410">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="B411">
-        <v>2008</v>
+        <v>1975</v>
       </c>
       <c r="C411" t="s">
         <v>36</v>
       </c>
-      <c r="D411" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E411" s="4"/>
+      <c r="D411">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>393</v>
+        <v>45</v>
       </c>
       <c r="B412">
-        <v>2008</v>
+        <v>1974</v>
       </c>
       <c r="C412" t="s">
         <v>36</v>
       </c>
-      <c r="D412" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E412" s="4"/>
-      <c r="F412" t="s">
-        <v>476</v>
+      <c r="D412">
+        <v>9.9</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="B413">
-        <v>2010</v>
+        <v>1973</v>
       </c>
       <c r="C413" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E413" s="4"/>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>305</v>
+        <v>179</v>
       </c>
       <c r="B414">
-        <v>2010</v>
+        <v>1973</v>
       </c>
       <c r="C414" t="s">
         <v>36</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E414" s="4"/>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="B415">
-        <v>2011</v>
+        <v>1973</v>
       </c>
       <c r="C415" t="s">
         <v>36</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E415" s="4"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>402</v>
+        <v>38</v>
       </c>
       <c r="B416">
-        <v>2011</v>
+        <v>1972</v>
       </c>
       <c r="C416" t="s">
         <v>36</v>
       </c>
-      <c r="D416" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E416" s="4"/>
+      <c r="D416">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="B417">
-        <v>2012</v>
+        <v>1972</v>
       </c>
       <c r="C417" t="s">
         <v>36</v>
       </c>
-      <c r="D417" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E417" s="4"/>
+      <c r="D417">
+        <v>7</v>
+      </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>280</v>
+        <v>58</v>
       </c>
       <c r="B418">
-        <v>2013</v>
+        <v>1971</v>
       </c>
       <c r="C418" t="s">
         <v>36</v>
       </c>
-      <c r="D418" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E418" s="4"/>
+      <c r="D418">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>146</v>
+        <v>337</v>
       </c>
       <c r="B419">
-        <v>2013</v>
+        <v>1971</v>
       </c>
       <c r="C419" t="s">
         <v>36</v>
       </c>
-      <c r="D419" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E419" s="4"/>
+      <c r="D419">
+        <v>7</v>
+      </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>255</v>
+        <v>70</v>
       </c>
       <c r="B420">
-        <v>2013</v>
+        <v>1968</v>
       </c>
       <c r="C420" t="s">
         <v>36</v>
       </c>
-      <c r="D420" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E420" s="4"/>
+      <c r="D420">
+        <v>10</v>
+      </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="B421">
-        <v>2014</v>
+        <v>1968</v>
       </c>
       <c r="C421" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E421" s="4"/>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="B422">
-        <v>2015</v>
+        <v>1968</v>
       </c>
       <c r="C422" t="s">
         <v>36</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E422" s="4"/>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>228</v>
+        <v>390</v>
       </c>
       <c r="B423">
-        <v>2015</v>
+        <v>1968</v>
       </c>
       <c r="C423" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E423" s="4"/>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>338</v>
+        <v>7</v>
       </c>
       <c r="B424">
-        <v>2015</v>
+        <v>1966</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
       </c>
-      <c r="D424" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E424" s="4"/>
+      <c r="D424">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="B425">
-        <v>2015</v>
+        <v>1965</v>
       </c>
       <c r="C425" t="s">
         <v>36</v>
       </c>
-      <c r="D425" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E425" s="4"/>
+      <c r="D425">
+        <v>6</v>
+      </c>
+      <c r="F425" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>284</v>
+        <v>358</v>
       </c>
       <c r="B426">
-        <v>2015</v>
+        <v>1963</v>
       </c>
       <c r="C426" t="s">
         <v>36</v>
       </c>
-      <c r="D426" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E426" s="4"/>
+      <c r="D426">
+        <v>7</v>
+      </c>
       <c r="F426" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B427">
-        <v>2016</v>
+        <v>1963</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E427" s="4"/>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>254</v>
+        <v>129</v>
       </c>
       <c r="B428">
-        <v>2016</v>
+        <v>1962</v>
       </c>
       <c r="C428" t="s">
         <v>36</v>
       </c>
-      <c r="D428" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E428" s="4"/>
+      <c r="D428">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="B429">
-        <v>2017</v>
+        <v>1960</v>
       </c>
       <c r="C429" t="s">
-        <v>5</v>
-      </c>
-      <c r="D429" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E429" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D429">
+        <v>7</v>
+      </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="2" t="s">
-        <v>452</v>
+      <c r="A430" t="s">
+        <v>171</v>
       </c>
       <c r="B430">
-        <v>2019</v>
+        <v>1959</v>
       </c>
       <c r="C430" t="s">
         <v>36</v>
       </c>
-      <c r="D430" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E430" s="4"/>
+      <c r="D430">
+        <v>7</v>
+      </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>265</v>
+        <v>4</v>
       </c>
       <c r="B431">
-        <v>2019</v>
+        <v>1957</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E431" s="4"/>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>373</v>
+        <v>15</v>
       </c>
       <c r="B432">
-        <v>2019</v>
+        <v>1954</v>
       </c>
       <c r="C432" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E432" s="4"/>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>253</v>
+        <v>11</v>
       </c>
       <c r="B433">
-        <v>2021</v>
+        <v>1954</v>
       </c>
       <c r="C433" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E433" s="4"/>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="B434">
-        <v>2021</v>
+        <v>1951</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E434" s="4"/>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="B435">
-        <v>2022</v>
+        <v>1950</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E435" s="4"/>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>541</v>
+        <v>9</v>
+      </c>
+      <c r="B436">
+        <v>1946</v>
       </c>
       <c r="C436" t="s">
-        <v>36</v>
-      </c>
-      <c r="D436" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E436" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D436">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>539</v>
+        <v>187</v>
+      </c>
+      <c r="B437">
+        <v>1939</v>
       </c>
       <c r="C437" t="s">
         <v>36</v>
       </c>
-      <c r="D437" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E437" s="4"/>
+      <c r="D437">
+        <v>9</v>
+      </c>
+      <c r="F437" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>540</v>
-      </c>
-      <c r="C438" t="s">
-        <v>36</v>
-      </c>
-      <c r="D438" s="4" t="s">
-        <v>548</v>
-      </c>
+      <c r="D438" s="4"/>
       <c r="E438" s="4"/>
-    </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
-        <v>451</v>
-      </c>
-      <c r="C439" t="s">
-        <v>36</v>
-      </c>
-      <c r="D439" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E439" s="4"/>
-      <c r="F439" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
-        <v>547</v>
-      </c>
-      <c r="C440" t="s">
-        <v>36</v>
-      </c>
-      <c r="D440" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E440" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A217:H401">
@@ -8564,7 +8587,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -8573,12 +8596,12 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -8586,7 +8609,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -8594,7 +8617,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -8602,7 +8625,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -8610,7 +8633,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -8618,7 +8641,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -8626,29 +8649,29 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C8">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C9">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -8656,7 +8679,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -8664,7 +8687,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -8672,7 +8695,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -8680,7 +8703,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -8688,7 +8711,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B15">
         <v>2011</v>
@@ -8697,23 +8720,23 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C16">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -8721,7 +8744,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -8729,7 +8752,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -8737,18 +8760,18 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C20">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C21">
         <v>7.5</v>
@@ -8756,7 +8779,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C22">
         <v>7.5</v>
@@ -8764,7 +8787,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C23">
         <v>7.5</v>
@@ -8772,7 +8795,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -8780,7 +8803,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -8788,7 +8811,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -8796,7 +8819,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -8804,7 +8827,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -8812,7 +8835,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -8820,7 +8843,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -8828,7 +8851,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C31">
         <v>6.5</v>
@@ -8836,29 +8859,29 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C32">
         <v>5.5</v>
       </c>
       <c r="D32" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B34">
         <v>2014</v>
@@ -8867,23 +8890,23 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -8923,13 +8946,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -8949,29 +8972,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B3" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Movies and Music.xlsx
+++ b/Movies and Music.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kroon\.gemini\antigravity\playground\Books Movies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kroon\.gemini\antigravity\playground\- DEPLOYED\Books Movies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5CF50F-3B0F-49C4-AD19-E68ABFA3DD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF69F56-A24D-49BC-981A-AA4E51E4005D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="559">
   <si>
     <t>Rating</t>
   </si>
@@ -1671,9 +1671,6 @@
     <t>Warriors</t>
   </si>
   <si>
-    <t>unrated</t>
-  </si>
-  <si>
     <t>Got weird</t>
   </si>
   <si>
@@ -1686,9 +1683,6 @@
     <t>Director</t>
   </si>
   <si>
-    <t>Loose Change</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -1698,12 +1692,6 @@
     <t>Link</t>
   </si>
   <si>
-    <t>Everything is a Rich Man's Trick</t>
-  </si>
-  <si>
-    <t>Tin Foil</t>
-  </si>
-  <si>
     <t>300</t>
   </si>
   <si>
@@ -1720,6 +1708,18 @@
   </si>
   <si>
     <t>Rich actors pretending to dislike the rich</t>
+  </si>
+  <si>
+    <t>The Fountainhead</t>
+  </si>
+  <si>
+    <t>Ayn Rand</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>Coming Soon</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>222</v>
@@ -2159,770 +2159,716 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>2024</v>
+        <v>2001</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
       </c>
       <c r="D2">
-        <v>8.3000000000000007</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B3">
-        <v>2024</v>
+        <v>1980</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>70</v>
       </c>
       <c r="B4">
-        <v>2024</v>
+        <v>1968</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>407</v>
       </c>
       <c r="B5">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>6.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>441</v>
+        <v>88</v>
       </c>
       <c r="B6">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>6.5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>440</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>47</v>
       </c>
       <c r="B7">
-        <v>2024</v>
+        <v>2003</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="F7" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>93</v>
       </c>
       <c r="B8">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>434</v>
+        <v>55</v>
       </c>
       <c r="B9">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>9.9</v>
       </c>
       <c r="F9" t="s">
-        <v>432</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>435</v>
+        <v>273</v>
       </c>
       <c r="B10">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>432</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>410</v>
+        <v>175</v>
       </c>
       <c r="B11">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>482</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>56</v>
       </c>
       <c r="B12">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12">
-        <v>4.5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>424</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="B13">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13">
-        <v>4.5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>426</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>86</v>
       </c>
       <c r="B14">
-        <v>2024</v>
+        <v>1987</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>420</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>442</v>
+        <v>51</v>
       </c>
       <c r="B15">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15">
-        <v>3.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>2023</v>
+        <v>1985</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B17">
-        <v>2023</v>
+        <v>1982</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="B18">
-        <v>2022</v>
+        <v>1981</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
       <c r="D18">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>525</v>
+        <v>46</v>
       </c>
       <c r="B19">
-        <v>2022</v>
+        <v>1979</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19">
-        <v>8.5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>45</v>
       </c>
       <c r="B20">
-        <v>2022</v>
+        <v>1974</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
       <c r="B21">
-        <v>2022</v>
+        <v>1972</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>508</v>
+        <v>41</v>
       </c>
       <c r="B22">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22">
-        <v>5.5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B23">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D23">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>411</v>
+        <v>238</v>
       </c>
       <c r="B24">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
       </c>
       <c r="D24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>413</v>
+        <v>50</v>
       </c>
       <c r="B25">
-        <v>2022</v>
+        <v>1994</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>557</v>
+        <v>57</v>
       </c>
       <c r="B26">
-        <v>2022</v>
+        <v>1982</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
       <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>354</v>
       </c>
       <c r="B27">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>252</v>
+        <v>128</v>
       </c>
       <c r="B29">
-        <v>2021</v>
+        <v>1983</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B30">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="B31">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>237</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="D32">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="B33">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D33">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B34">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>339</v>
+        <v>155</v>
       </c>
       <c r="B35">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="C35" t="s">
         <v>36</v>
       </c>
       <c r="D35">
-        <v>7.5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="B36">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="C36" t="s">
         <v>36</v>
       </c>
       <c r="D36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>349</v>
+        <v>141</v>
       </c>
       <c r="B37">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="C37" t="s">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="B38">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
       </c>
       <c r="D38">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>449</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="C39" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
       <c r="B41">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="B42">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="C42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43">
+        <v>1994</v>
+      </c>
+      <c r="C43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44">
+        <v>1994</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45">
+        <v>1993</v>
+      </c>
+      <c r="C45" t="s">
         <v>27</v>
       </c>
-      <c r="D42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43">
-        <v>2018</v>
-      </c>
-      <c r="C43" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44">
-        <v>2018</v>
-      </c>
-      <c r="C44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45">
-        <v>2018</v>
-      </c>
-      <c r="C45" t="s">
-        <v>36</v>
-      </c>
       <c r="D45">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>334</v>
+        <v>127</v>
       </c>
       <c r="B46">
-        <v>2018</v>
+        <v>1992</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
       </c>
       <c r="D46">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="B47">
-        <v>2018</v>
+        <v>1991</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D47">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>352</v>
+        <v>29</v>
       </c>
       <c r="B48">
-        <v>2018</v>
+        <v>1991</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="B49">
-        <v>2018</v>
+        <v>1990</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>304</v>
+        <v>169</v>
       </c>
       <c r="B50">
-        <v>2018</v>
+        <v>1989</v>
       </c>
       <c r="C50" t="s">
         <v>36</v>
       </c>
       <c r="D50">
-        <v>4.5</v>
-      </c>
-      <c r="F50" t="s">
-        <v>425</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>354</v>
+        <v>538</v>
       </c>
       <c r="B51">
-        <v>2017</v>
+        <v>1988</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D51">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="B52">
-        <v>2017</v>
+        <v>1987</v>
       </c>
       <c r="C52" t="s">
         <v>36</v>
@@ -2933,466 +2879,462 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>257</v>
       </c>
       <c r="B53">
-        <v>2017</v>
+        <v>1986</v>
       </c>
       <c r="C53" t="s">
         <v>36</v>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>373</v>
       </c>
       <c r="B54">
-        <v>2017</v>
+        <v>1984</v>
       </c>
       <c r="C54" t="s">
         <v>36</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>319</v>
+        <v>61</v>
       </c>
       <c r="B55">
-        <v>2017</v>
+        <v>1984</v>
       </c>
       <c r="C55" t="s">
         <v>36</v>
       </c>
       <c r="D55">
-        <v>6.5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>475</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>290</v>
+        <v>103</v>
       </c>
       <c r="B56">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="B57">
-        <v>2017</v>
+        <v>1977</v>
       </c>
       <c r="C57" t="s">
         <v>36</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B58">
-        <v>2017</v>
+        <v>1975</v>
       </c>
       <c r="C58" t="s">
         <v>36</v>
       </c>
       <c r="D58">
-        <v>4</v>
-      </c>
-      <c r="F58" t="s">
-        <v>421</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B59">
-        <v>2017</v>
+        <v>1939</v>
       </c>
       <c r="C59" t="s">
         <v>36</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>525</v>
       </c>
       <c r="B60">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C60" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E60" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D60">
+        <v>8.5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>140</v>
+        <v>392</v>
       </c>
       <c r="B61">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
       </c>
       <c r="D61">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="B62">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
       <c r="D62">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>397</v>
+        <v>109</v>
       </c>
       <c r="B63">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="C63" t="s">
         <v>36</v>
       </c>
       <c r="D63">
-        <v>6.5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>432</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="B64">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
       </c>
       <c r="D64">
-        <v>6.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="B65">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="C65" t="s">
         <v>36</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="F65" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="B66">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="C66" t="s">
         <v>36</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>69</v>
       </c>
       <c r="B67">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="B68">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C68" t="s">
         <v>36</v>
       </c>
       <c r="D68">
-        <v>4</v>
-      </c>
-      <c r="F68" t="s">
-        <v>422</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B69">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D69">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="B70">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C70" t="s">
         <v>36</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E70" s="4"/>
+      <c r="D70">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B71">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C71" t="s">
         <v>36</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="B72">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="C72" t="s">
         <v>36</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>394</v>
       </c>
       <c r="B73">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C73" t="s">
         <v>36</v>
       </c>
       <c r="D73">
-        <v>7.6</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F73" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B74">
-        <v>2015</v>
+        <v>2003</v>
       </c>
       <c r="C74" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D74">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="B75">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="C75" t="s">
         <v>36</v>
       </c>
       <c r="D75">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>438</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>220</v>
       </c>
       <c r="B76">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="C76" t="s">
         <v>36</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>278</v>
+        <v>96</v>
       </c>
       <c r="B77">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="s">
         <v>36</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="B78">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C78" t="s">
         <v>36</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F78" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>182</v>
+        <v>411</v>
       </c>
       <c r="B79">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C79" t="s">
         <v>36</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>340</v>
+        <v>64</v>
       </c>
       <c r="B80">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C80" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E80" s="4"/>
+      <c r="D80">
+        <v>8</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="B81">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C81" t="s">
         <v>36</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E81" s="4"/>
+      <c r="D81">
+        <v>8</v>
+      </c>
+      <c r="F81" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>336</v>
+        <v>87</v>
       </c>
       <c r="B82">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C82" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E82" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D82">
+        <v>8</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="B83">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E83" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D83">
+        <v>8</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="B84">
         <v>2015</v>
@@ -3400,45 +3342,41 @@
       <c r="C84" t="s">
         <v>36</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E84" s="4"/>
-      <c r="F84" t="s">
-        <v>469</v>
+      <c r="D84">
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>407</v>
+        <v>68</v>
       </c>
       <c r="B85">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="B86">
         <v>2014</v>
       </c>
       <c r="C86" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D86">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B87">
         <v>2014</v>
@@ -3447,18 +3385,18 @@
         <v>36</v>
       </c>
       <c r="D87">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>299</v>
+        <v>193</v>
       </c>
       <c r="B88">
         <v>2014</v>
       </c>
       <c r="C88" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D88">
         <v>8</v>
@@ -3466,10 +3404,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B89">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
@@ -3480,751 +3418,739 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="B90">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>8</v>
       </c>
+      <c r="F90" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>293</v>
+        <v>139</v>
       </c>
       <c r="B91">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C91" t="s">
         <v>36</v>
       </c>
       <c r="D91">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="B92">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C92" t="s">
         <v>36</v>
       </c>
       <c r="D92">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>66</v>
+      <c r="A93" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="B93">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C93" t="s">
         <v>36</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>351</v>
+        <v>167</v>
       </c>
       <c r="B94">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B95">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C95" t="s">
         <v>36</v>
       </c>
       <c r="D95">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>468</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="B96">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C96" t="s">
         <v>36</v>
       </c>
       <c r="D96">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>243</v>
+        <v>32</v>
       </c>
       <c r="B97">
-        <v>2014</v>
+        <v>2002</v>
       </c>
       <c r="C97" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D97">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="B98">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C98" t="s">
         <v>36</v>
       </c>
       <c r="D98">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>190</v>
+        <v>457</v>
       </c>
       <c r="B99">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C99" t="s">
         <v>36</v>
       </c>
       <c r="D99">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="B100">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="C100" t="s">
         <v>36</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E100" s="4"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>412</v>
+        <v>206</v>
       </c>
       <c r="B101">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="C101" t="s">
         <v>36</v>
       </c>
       <c r="D101">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>287</v>
+        <v>154</v>
       </c>
       <c r="B102">
-        <v>2013</v>
+        <v>1999</v>
       </c>
       <c r="C102" t="s">
         <v>36</v>
       </c>
       <c r="D102">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>294</v>
+        <v>427</v>
       </c>
       <c r="B103">
-        <v>2013</v>
+        <v>1999</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="B104">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C104" t="s">
+        <v>36</v>
+      </c>
+      <c r="D104">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105">
+        <v>1997</v>
+      </c>
+      <c r="C105" t="s">
         <v>27</v>
       </c>
-      <c r="D104">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>67</v>
-      </c>
-      <c r="B105">
-        <v>2013</v>
-      </c>
-      <c r="C105" t="s">
-        <v>36</v>
-      </c>
       <c r="D105">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B106">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="C106" t="s">
         <v>36</v>
       </c>
       <c r="D106">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B107">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="C107" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D107">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="B108">
-        <v>2013</v>
+        <v>1996</v>
       </c>
       <c r="C108" t="s">
         <v>36</v>
       </c>
       <c r="D108">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="B109">
-        <v>2013</v>
+        <v>1995</v>
       </c>
       <c r="C109" t="s">
         <v>36</v>
       </c>
       <c r="D109">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>428</v>
       </c>
       <c r="B110">
-        <v>2013</v>
+        <v>1995</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D110">
-        <v>3</v>
-      </c>
-      <c r="F110" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>279</v>
+        <v>35</v>
       </c>
       <c r="B111">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="C111" t="s">
         <v>36</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E111" s="4"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>146</v>
+        <v>456</v>
       </c>
       <c r="B112">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="C112" t="s">
         <v>36</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E112" s="4"/>
+      <c r="D112">
+        <v>8</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="B113">
-        <v>2013</v>
+        <v>1991</v>
       </c>
       <c r="C113" t="s">
         <v>36</v>
       </c>
-      <c r="D113" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E113" s="4"/>
+      <c r="D113">
+        <v>8</v>
+      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="B114">
-        <v>2012</v>
+        <v>1991</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D114">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>183</v>
+        <v>341</v>
       </c>
       <c r="B115">
-        <v>2012</v>
+        <v>1990</v>
       </c>
       <c r="C115" t="s">
         <v>36</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F115" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B116">
-        <v>2012</v>
+        <v>1990</v>
       </c>
       <c r="C116" t="s">
         <v>36</v>
       </c>
       <c r="D116">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>372</v>
       </c>
       <c r="B117">
-        <v>2012</v>
+        <v>1990</v>
       </c>
       <c r="C117" t="s">
         <v>36</v>
       </c>
       <c r="D117">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="B118">
-        <v>2012</v>
+        <v>1990</v>
       </c>
       <c r="C118" t="s">
         <v>36</v>
       </c>
       <c r="D118">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>388</v>
       </c>
       <c r="B119">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="C119" t="s">
         <v>36</v>
       </c>
       <c r="D119">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>173</v>
+        <v>443</v>
       </c>
       <c r="B120">
-        <v>2012</v>
+        <v>1979</v>
       </c>
       <c r="C120" t="s">
         <v>36</v>
       </c>
       <c r="D120">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>106</v>
+        <v>409</v>
       </c>
       <c r="B121">
-        <v>2012</v>
+        <v>1978</v>
       </c>
       <c r="C121" t="s">
         <v>36</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F121" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B122">
-        <v>2012</v>
+        <v>1976</v>
       </c>
       <c r="C122" t="s">
         <v>36</v>
       </c>
-      <c r="D122" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E122" s="4"/>
+      <c r="D122">
+        <v>8</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="B123">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C123" t="s">
         <v>36</v>
       </c>
       <c r="D123">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>346</v>
+        <v>161</v>
       </c>
       <c r="B124">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="C124" t="s">
         <v>36</v>
       </c>
       <c r="D124">
-        <v>7</v>
-      </c>
-      <c r="F124" t="s">
-        <v>454</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>176</v>
+        <v>271</v>
       </c>
       <c r="B125">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C125" t="s">
         <v>36</v>
       </c>
       <c r="D125">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="B126">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C126" t="s">
         <v>36</v>
       </c>
       <c r="D126">
-        <v>6</v>
+        <v>7.5</v>
+      </c>
+      <c r="F126" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>317</v>
+        <v>140</v>
       </c>
       <c r="B127">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C127" t="s">
         <v>36</v>
       </c>
-      <c r="D127" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E127" s="4"/>
+      <c r="D127">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>400</v>
+        <v>314</v>
       </c>
       <c r="B128">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C128" t="s">
         <v>36</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E128" s="4"/>
+      <c r="D128">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>405</v>
       </c>
       <c r="B129">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C129" t="s">
         <v>36</v>
       </c>
       <c r="D129">
-        <v>8.3000000000000007</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="B130">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C130" t="s">
         <v>36</v>
       </c>
       <c r="D130">
-        <v>7</v>
-      </c>
-      <c r="F130" t="s">
-        <v>464</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="B131">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C131" t="s">
         <v>36</v>
       </c>
       <c r="D131">
-        <v>7</v>
-      </c>
-      <c r="F131" t="s">
-        <v>458</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>200</v>
+        <v>412</v>
       </c>
       <c r="B132">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C132" t="s">
         <v>36</v>
       </c>
       <c r="D132">
-        <v>7</v>
-      </c>
-      <c r="F132" t="s">
-        <v>467</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="B133">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C133" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D133">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>404</v>
+        <v>114</v>
       </c>
       <c r="B134">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C134" t="s">
         <v>36</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="B135">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C135" t="s">
         <v>36</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>280</v>
+        <v>52</v>
       </c>
       <c r="B136">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C136" t="s">
         <v>36</v>
       </c>
-      <c r="D136" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E136" s="4"/>
+      <c r="D136">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>303</v>
+        <v>150</v>
       </c>
       <c r="B137">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C137" t="s">
         <v>36</v>
       </c>
-      <c r="D137" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E137" s="4"/>
+      <c r="D137">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="B138">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C138" t="s">
         <v>36</v>
       </c>
       <c r="D138">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="B139">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C139" t="s">
         <v>36</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>7.5</v>
+      </c>
+      <c r="F139" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>76</v>
+        <v>403</v>
       </c>
       <c r="B140">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="C140" t="s">
         <v>36</v>
       </c>
       <c r="D140">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="B141">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="C141" t="s">
         <v>36</v>
@@ -4235,83 +4161,80 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="B142">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C142" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>285</v>
+        <v>552</v>
       </c>
       <c r="B143">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C143" t="s">
         <v>36</v>
       </c>
       <c r="D143">
-        <v>6</v>
-      </c>
-      <c r="F143" t="s">
-        <v>463</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="B144">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C144" t="s">
         <v>36</v>
       </c>
       <c r="D144">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="B145">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="C145" t="s">
         <v>36</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="B146">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="C146" t="s">
         <v>36</v>
       </c>
       <c r="D146">
-        <v>9.6999999999999993</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>52</v>
+        <v>289</v>
       </c>
       <c r="B147">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="C147" t="s">
         <v>36</v>
@@ -4319,178 +4242,176 @@
       <c r="D147">
         <v>7.5</v>
       </c>
+      <c r="F147" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="B148">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="C148" t="s">
         <v>36</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>7.5</v>
+      </c>
+      <c r="F148" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>381</v>
+        <v>130</v>
       </c>
       <c r="B149">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="C149" t="s">
         <v>36</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="B150">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="C150" t="s">
         <v>36</v>
       </c>
       <c r="D150">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="B151">
-        <v>2008</v>
+        <v>1996</v>
       </c>
       <c r="C151" t="s">
         <v>36</v>
       </c>
       <c r="D151">
-        <v>6.5</v>
-      </c>
-      <c r="F151" t="s">
-        <v>459</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="B152">
-        <v>2008</v>
+        <v>1995</v>
       </c>
       <c r="C152" t="s">
         <v>36</v>
       </c>
       <c r="D152">
-        <v>4.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="F152" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="B153">
-        <v>2008</v>
+        <v>1992</v>
       </c>
       <c r="C153" t="s">
         <v>36</v>
       </c>
-      <c r="D153" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E153" s="4"/>
+      <c r="D153">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>391</v>
+        <v>126</v>
       </c>
       <c r="B154">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="C154" t="s">
         <v>36</v>
       </c>
-      <c r="D154" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E154" s="4"/>
-      <c r="F154" t="s">
-        <v>473</v>
+      <c r="D154">
+        <v>7.5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B155">
-        <v>2007</v>
+        <v>1990</v>
       </c>
       <c r="C155" t="s">
         <v>36</v>
       </c>
       <c r="D155">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>230</v>
+        <v>375</v>
       </c>
       <c r="B156">
-        <v>2007</v>
+        <v>1990</v>
       </c>
       <c r="C156" t="s">
         <v>36</v>
       </c>
       <c r="D156">
-        <v>8.3000000000000007</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="B157">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="C157" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D157">
-        <v>8</v>
-      </c>
-      <c r="F157" t="s">
-        <v>530</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="B158">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="C158" t="s">
         <v>36</v>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="B159">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="C159" t="s">
         <v>36</v>
@@ -4501,38 +4422,39 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>143</v>
+        <v>384</v>
       </c>
       <c r="B160">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="C160" t="s">
         <v>36</v>
       </c>
       <c r="D160">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>241</v>
+        <v>534</v>
       </c>
       <c r="B161">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="C161" t="s">
         <v>36</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="4">
         <v>7.5</v>
       </c>
+      <c r="E161" s="4"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>406</v>
+        <v>256</v>
       </c>
       <c r="B162">
-        <v>2007</v>
+        <v>1985</v>
       </c>
       <c r="C162" t="s">
         <v>36</v>
@@ -4540,364 +4462,356 @@
       <c r="D162">
         <v>7.5</v>
       </c>
-      <c r="F162" t="s">
-        <v>455</v>
-      </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>365</v>
       </c>
       <c r="B163">
-        <v>2007</v>
+        <v>1984</v>
       </c>
       <c r="C163" t="s">
         <v>36</v>
       </c>
       <c r="D163">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>153</v>
+        <v>320</v>
       </c>
       <c r="B164">
-        <v>2007</v>
+        <v>1984</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E164" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D164">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>416</v>
+        <v>536</v>
       </c>
       <c r="B165">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="C165" t="s">
         <v>36</v>
       </c>
-      <c r="D165">
-        <v>8</v>
-      </c>
+      <c r="D165" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="E165" s="4"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="B166">
-        <v>2006</v>
+        <v>1980</v>
       </c>
       <c r="C166" t="s">
         <v>36</v>
       </c>
       <c r="D166">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="B167">
-        <v>2006</v>
+        <v>1978</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D167">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="F167" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>389</v>
+        <v>266</v>
       </c>
       <c r="B168">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="C168" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D168">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="B169">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="C169" t="s">
         <v>36</v>
       </c>
       <c r="D169">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>553</v>
+      <c r="A170" t="s">
+        <v>58</v>
       </c>
       <c r="B170">
-        <v>2006</v>
+        <v>1971</v>
       </c>
       <c r="C170" t="s">
         <v>36</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>554</v>
+        <v>7</v>
       </c>
       <c r="B171">
-        <v>2006</v>
+        <v>1966</v>
       </c>
       <c r="C171" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="B172">
-        <v>2006</v>
+        <v>1962</v>
       </c>
       <c r="C172" t="s">
         <v>36</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
       <c r="B173">
-        <v>2006</v>
+        <v>1946</v>
       </c>
       <c r="C173" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D173">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="B174">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="C174" t="s">
         <v>36</v>
       </c>
       <c r="D174">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="B175">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D175">
-        <v>4.5</v>
-      </c>
-      <c r="F175" t="s">
-        <v>408</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="B176">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="C176" t="s">
-        <v>5</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E176" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D176">
+        <v>7</v>
+      </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>347</v>
+        <v>413</v>
       </c>
       <c r="B177">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C177" t="s">
         <v>36</v>
       </c>
-      <c r="D177" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E177" s="4"/>
+      <c r="D177">
+        <v>7</v>
+      </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="B178">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="C178" t="s">
-        <v>5</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E178" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D178">
+        <v>7</v>
+      </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B179">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C179" t="s">
         <v>36</v>
       </c>
-      <c r="D179" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E179" s="4"/>
+      <c r="D179">
+        <v>7</v>
+      </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>307</v>
+        <v>237</v>
       </c>
       <c r="B180">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C180" t="s">
         <v>36</v>
       </c>
-      <c r="D180" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E180" s="4"/>
+      <c r="D180">
+        <v>7</v>
+      </c>
+      <c r="F180" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B181">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="C181" t="s">
         <v>36</v>
       </c>
       <c r="D181">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B182">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="C182" t="s">
         <v>36</v>
       </c>
       <c r="D182">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>392</v>
+        <v>151</v>
       </c>
       <c r="B183">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="C183" t="s">
         <v>36</v>
       </c>
       <c r="D183">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>394</v>
+        <v>92</v>
       </c>
       <c r="B184">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="C184" t="s">
         <v>36</v>
       </c>
       <c r="D184">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="F184" t="s">
-        <v>460</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="B185">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="C185" t="s">
         <v>36</v>
       </c>
       <c r="D185">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B186">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C186" t="s">
         <v>36</v>
       </c>
       <c r="D186">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>401</v>
+        <v>121</v>
       </c>
       <c r="B187">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C187" t="s">
         <v>36</v>
@@ -4908,24 +4822,27 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>380</v>
+        <v>202</v>
       </c>
       <c r="B188">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C188" t="s">
         <v>36</v>
       </c>
       <c r="D188">
         <v>7</v>
+      </c>
+      <c r="F188" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>398</v>
+        <v>148</v>
       </c>
       <c r="B189">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C189" t="s">
         <v>36</v>
@@ -4936,101 +4853,100 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>321</v>
+        <v>66</v>
       </c>
       <c r="B190">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="C190" t="s">
-        <v>5</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E190" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D190">
+        <v>7</v>
+      </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="B191">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="C191" t="s">
-        <v>36</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E191" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D191">
+        <v>7</v>
+      </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="B192">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="C192" t="s">
-        <v>5</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E192" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D192">
+        <v>7</v>
+      </c>
+      <c r="F192" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B193">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="C193" t="s">
-        <v>5</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E193" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D193">
+        <v>7</v>
+      </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>403</v>
+        <v>287</v>
       </c>
       <c r="B194">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C194" t="s">
         <v>36</v>
       </c>
       <c r="D194">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="B195">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C195" t="s">
         <v>36</v>
       </c>
       <c r="D195">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>376</v>
+        <v>302</v>
       </c>
       <c r="B196">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C196" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D196">
         <v>7</v>
@@ -5038,10 +4954,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>323</v>
+        <v>183</v>
       </c>
       <c r="B197">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C197" t="s">
         <v>36</v>
@@ -5052,278 +4968,274 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B198">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C198" t="s">
         <v>36</v>
       </c>
       <c r="D198">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>433</v>
+        <v>122</v>
       </c>
       <c r="B199">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C199" t="s">
         <v>36</v>
       </c>
       <c r="D199">
-        <v>6.5</v>
-      </c>
-      <c r="F199" t="s">
-        <v>432</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>399</v>
+        <v>346</v>
       </c>
       <c r="B200">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C200" t="s">
         <v>36</v>
       </c>
       <c r="D200">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F200" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>327</v>
+        <v>244</v>
       </c>
       <c r="B201">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C201" t="s">
         <v>36</v>
       </c>
       <c r="D201">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F201" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="B202">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C202" t="s">
         <v>36</v>
       </c>
-      <c r="D202" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E202" s="4"/>
+      <c r="D202">
+        <v>7</v>
+      </c>
+      <c r="F202" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="B203">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C203" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E203" s="4"/>
+      <c r="D203">
+        <v>7</v>
+      </c>
+      <c r="F203" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B204">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C204" t="s">
-        <v>36</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E204" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D204">
+        <v>7</v>
+      </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="B205">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="C205" t="s">
         <v>36</v>
       </c>
-      <c r="D205" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E205" s="4"/>
+      <c r="D205">
+        <v>7</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>386</v>
+        <v>166</v>
       </c>
       <c r="B206">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="C206" t="s">
         <v>36</v>
       </c>
-      <c r="D206" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E206" s="4"/>
+      <c r="D206">
+        <v>7</v>
+      </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>330</v>
+        <v>174</v>
       </c>
       <c r="B207">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C207" t="s">
         <v>36</v>
       </c>
-      <c r="D207" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E207" s="4"/>
+      <c r="D207">
+        <v>7</v>
+      </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>381</v>
       </c>
       <c r="B208">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C208" t="s">
         <v>36</v>
       </c>
-      <c r="D208" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E208" s="4"/>
+      <c r="D208">
+        <v>7</v>
+      </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>47</v>
+        <v>217</v>
       </c>
       <c r="B209">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="C209" t="s">
         <v>36</v>
       </c>
       <c r="D209">
-        <v>9.9</v>
-      </c>
-      <c r="F209" t="s">
-        <v>539</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B210">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C210" t="s">
         <v>36</v>
       </c>
       <c r="D210">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B211">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C211" t="s">
         <v>36</v>
       </c>
       <c r="D211">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>419</v>
+        <v>550</v>
       </c>
       <c r="B212">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="C212" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D212">
-        <v>8.3000000000000007</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B213">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="C213" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D213">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>556</v>
+        <v>401</v>
       </c>
       <c r="B214">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C214" t="s">
         <v>36</v>
       </c>
       <c r="D214">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>209</v>
+        <v>380</v>
       </c>
       <c r="B215">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C215" t="s">
         <v>36</v>
       </c>
       <c r="D215">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>124</v>
+        <v>398</v>
       </c>
       <c r="B216">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C216" t="s">
         <v>36</v>
@@ -5334,51 +5246,49 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="B217">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C217" t="s">
         <v>36</v>
       </c>
-      <c r="D217" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E217" s="4"/>
+      <c r="D217">
+        <v>7</v>
+      </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="B218">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C218" t="s">
         <v>36</v>
       </c>
-      <c r="D218" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E218" s="4"/>
+      <c r="D218">
+        <v>7</v>
+      </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B219">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C219" t="s">
         <v>36</v>
       </c>
       <c r="D219">
-        <v>9.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="B220">
         <v>2002</v>
@@ -5387,276 +5297,265 @@
         <v>36</v>
       </c>
       <c r="D220">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="F220" t="s">
-        <v>540</v>
+        <v>444</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>109</v>
+        <v>326</v>
       </c>
       <c r="B221">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C221" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D221">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>436</v>
+        <v>65</v>
       </c>
       <c r="B222">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C222" t="s">
         <v>36</v>
       </c>
       <c r="D222">
-        <v>8.5</v>
-      </c>
-      <c r="F222" t="s">
-        <v>437</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B223">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C223" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D223">
-        <v>8.5</v>
-      </c>
-      <c r="F223" t="s">
-        <v>481</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="B224">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C224" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D224">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F224" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B225">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C225" t="s">
         <v>36</v>
       </c>
       <c r="D225">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="B226">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C226" t="s">
         <v>36</v>
       </c>
       <c r="D226">
         <v>7</v>
-      </c>
-      <c r="F226" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>197</v>
+        <v>353</v>
       </c>
       <c r="B227">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C227" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D227">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F227" t="s">
-        <v>477</v>
+        <v>551</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>208</v>
+        <v>30</v>
       </c>
       <c r="B228">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C228" t="s">
-        <v>36</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E228" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D228">
+        <v>7</v>
+      </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B229">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C229" t="s">
-        <v>5</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E229" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D229">
+        <v>7</v>
+      </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>284</v>
+        <v>149</v>
       </c>
       <c r="B230">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C230" t="s">
         <v>36</v>
       </c>
-      <c r="D230" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E230" s="4"/>
+      <c r="D230">
+        <v>7</v>
+      </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>362</v>
+        <v>31</v>
       </c>
       <c r="B231">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C231" t="s">
-        <v>36</v>
-      </c>
-      <c r="D231" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E231" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D231">
+        <v>7</v>
+      </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B232">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C232" t="s">
         <v>36</v>
       </c>
-      <c r="D232" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E232" s="4"/>
+      <c r="D232">
+        <v>7</v>
+      </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B233">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C233" t="s">
         <v>36</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>260</v>
+        <v>430</v>
       </c>
       <c r="B234">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C234" t="s">
         <v>36</v>
       </c>
       <c r="D234">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B235">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="C235" t="s">
         <v>36</v>
       </c>
       <c r="D235">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>289</v>
+        <v>133</v>
       </c>
       <c r="B236">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="C236" t="s">
         <v>36</v>
       </c>
       <c r="D236">
-        <v>7.5</v>
-      </c>
-      <c r="F236" t="s">
-        <v>466</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B237">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="C237" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D237">
         <v>7</v>
+      </c>
+      <c r="F237" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="B238">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="C238" t="s">
         <v>36</v>
@@ -5667,39 +5566,41 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="B239">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="C239" t="s">
         <v>36</v>
       </c>
       <c r="D239">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>10</v>
+        <v>331</v>
       </c>
       <c r="B240">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="C240" t="s">
-        <v>5</v>
-      </c>
-      <c r="D240" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E240" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D240">
+        <v>7</v>
+      </c>
+      <c r="F240" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>476</v>
+        <v>274</v>
       </c>
       <c r="B241">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="C241" t="s">
         <v>27</v>
@@ -5710,83 +5611,81 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>457</v>
+        <v>369</v>
       </c>
       <c r="B242">
-        <v>2001</v>
+        <v>1989</v>
       </c>
       <c r="C242" t="s">
         <v>36</v>
       </c>
       <c r="D242">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="B243">
-        <v>2000</v>
+        <v>1989</v>
       </c>
       <c r="C243" t="s">
         <v>36</v>
       </c>
       <c r="D243">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>160</v>
+        <v>378</v>
       </c>
       <c r="B244">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="C244" t="s">
         <v>36</v>
       </c>
       <c r="D244">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>135</v>
+        <v>535</v>
       </c>
       <c r="B245">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="C245" t="s">
         <v>36</v>
       </c>
-      <c r="D245">
-        <v>7.5</v>
-      </c>
-      <c r="F245" t="s">
-        <v>472</v>
-      </c>
+      <c r="D245" s="4">
+        <v>7</v>
+      </c>
+      <c r="E245" s="4"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="B246">
-        <v>2000</v>
+        <v>1987</v>
       </c>
       <c r="C246" t="s">
         <v>36</v>
       </c>
       <c r="D246">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>228</v>
+        <v>377</v>
       </c>
       <c r="B247">
-        <v>2000</v>
+        <v>1986</v>
       </c>
       <c r="C247" t="s">
         <v>36</v>
@@ -5795,18 +5694,18 @@
         <v>7</v>
       </c>
       <c r="F247" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>178</v>
+        <v>313</v>
       </c>
       <c r="B248">
-        <v>2000</v>
+        <v>1985</v>
       </c>
       <c r="C248" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D248">
         <v>7</v>
@@ -5814,155 +5713,159 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>328</v>
+        <v>249</v>
       </c>
       <c r="B249">
-        <v>2000</v>
+        <v>1984</v>
       </c>
       <c r="C249" t="s">
         <v>36</v>
       </c>
-      <c r="D249" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E249" s="4"/>
+      <c r="D249">
+        <v>7</v>
+      </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>111</v>
+        <v>541</v>
       </c>
       <c r="B250">
-        <v>2000</v>
+        <v>1979</v>
       </c>
       <c r="C250" t="s">
-        <v>36</v>
-      </c>
-      <c r="D250" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E250" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D250">
+        <v>7</v>
+      </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c r="B251">
-        <v>1999</v>
+        <v>1978</v>
       </c>
       <c r="C251" t="s">
         <v>36</v>
       </c>
       <c r="D251">
-        <v>9.9</v>
+        <v>7</v>
+      </c>
+      <c r="F251" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>53</v>
+        <v>315</v>
       </c>
       <c r="B252">
-        <v>1999</v>
+        <v>1972</v>
       </c>
       <c r="C252" t="s">
         <v>36</v>
       </c>
       <c r="D252">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>40</v>
+        <v>337</v>
       </c>
       <c r="B253">
-        <v>1999</v>
+        <v>1971</v>
       </c>
       <c r="C253" t="s">
         <v>36</v>
       </c>
       <c r="D253">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>186</v>
+        <v>358</v>
       </c>
       <c r="B254">
-        <v>1999</v>
+        <v>1963</v>
       </c>
       <c r="C254" t="s">
         <v>36</v>
       </c>
       <c r="D254">
         <v>7</v>
+      </c>
+      <c r="F254" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>206</v>
+        <v>95</v>
       </c>
       <c r="B255">
-        <v>1999</v>
+        <v>1960</v>
       </c>
       <c r="C255" t="s">
         <v>36</v>
       </c>
       <c r="D255">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B256">
-        <v>1999</v>
+        <v>1959</v>
       </c>
       <c r="C256" t="s">
         <v>36</v>
       </c>
       <c r="D256">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>353</v>
+        <v>245</v>
       </c>
       <c r="B257">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D257">
-        <v>7</v>
-      </c>
-      <c r="F257" t="s">
-        <v>555</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>30</v>
+        <v>441</v>
       </c>
       <c r="B258">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="C258" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D258">
-        <v>7</v>
+        <v>6.5</v>
+      </c>
+      <c r="F258" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B259">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="C259" t="s">
         <v>36</v>
@@ -5973,218 +5876,229 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="B260">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="C260" t="s">
         <v>36</v>
       </c>
-      <c r="D260" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E260" s="4"/>
+      <c r="D260">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>427</v>
+        <v>348</v>
       </c>
       <c r="B261">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="C261" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D261">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B262">
-        <v>1998</v>
+        <v>2017</v>
       </c>
       <c r="C262" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>6.5</v>
+      </c>
+      <c r="F262" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>198</v>
+        <v>397</v>
       </c>
       <c r="B263">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="C263" t="s">
         <v>36</v>
       </c>
       <c r="D263">
-        <v>8</v>
+        <v>6.5</v>
+      </c>
+      <c r="F263" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="B264">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="C264" t="s">
         <v>36</v>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>147</v>
+        <v>243</v>
       </c>
       <c r="B265">
-        <v>1998</v>
+        <v>2014</v>
       </c>
       <c r="C265" t="s">
         <v>36</v>
       </c>
       <c r="D265">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="B266">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="C266" t="s">
         <v>36</v>
       </c>
       <c r="D266">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B267">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="C267" t="s">
         <v>36</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>31</v>
+        <v>393</v>
       </c>
       <c r="B268">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="C268" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D268">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B269">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="C269" t="s">
         <v>36</v>
       </c>
       <c r="D269">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>180</v>
+        <v>343</v>
       </c>
       <c r="B270">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C270" t="s">
         <v>36</v>
       </c>
       <c r="D270">
-        <v>7</v>
+        <v>6.5</v>
+      </c>
+      <c r="F270" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>204</v>
+        <v>117</v>
       </c>
       <c r="B271">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C271" t="s">
         <v>36</v>
       </c>
       <c r="D271">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B272">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C272" t="s">
         <v>36</v>
       </c>
       <c r="D272">
-        <v>7</v>
+        <v>6.5</v>
+      </c>
+      <c r="F272" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="B273">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C273" t="s">
         <v>36</v>
       </c>
       <c r="D273">
-        <v>9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>34</v>
+        <v>291</v>
       </c>
       <c r="B274">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C274" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D274">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>131</v>
+        <v>385</v>
       </c>
       <c r="B275">
         <v>1997</v>
@@ -6193,12 +6107,15 @@
         <v>36</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>6.5</v>
+      </c>
+      <c r="F275" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B276">
         <v>1997</v>
@@ -6210,43 +6127,46 @@
         <v>6.5</v>
       </c>
       <c r="F276" t="s">
-        <v>478</v>
+        <v>415</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="B277">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="C277" t="s">
         <v>36</v>
       </c>
       <c r="D277">
-        <v>7</v>
+        <v>6.5</v>
+      </c>
+      <c r="F277" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="B278">
-        <v>1997</v>
+        <v>1988</v>
       </c>
       <c r="C278" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D278">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>374</v>
+        <v>537</v>
       </c>
       <c r="B279">
-        <v>1997</v>
+        <v>1977</v>
       </c>
       <c r="C279" t="s">
         <v>36</v>
@@ -6254,16 +6174,13 @@
       <c r="D279">
         <v>6.5</v>
       </c>
-      <c r="F279" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>134</v>
+        <v>506</v>
       </c>
       <c r="B280">
-        <v>1997</v>
+        <v>2024</v>
       </c>
       <c r="C280" t="s">
         <v>36</v>
@@ -6271,539 +6188,553 @@
       <c r="D280">
         <v>6</v>
       </c>
+      <c r="F280" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="B281">
-        <v>1997</v>
+        <v>2024</v>
       </c>
       <c r="C281" t="s">
-        <v>36</v>
-      </c>
-      <c r="D281" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E281" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D281">
+        <v>6</v>
+      </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>18</v>
+        <v>553</v>
       </c>
       <c r="B282">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="C282" t="s">
-        <v>5</v>
-      </c>
-      <c r="D282" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E282" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D282">
+        <v>6</v>
+      </c>
+      <c r="F282" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>329</v>
+        <v>192</v>
       </c>
       <c r="B283">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="C283" t="s">
         <v>36</v>
       </c>
-      <c r="D283" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E283" s="4"/>
+      <c r="D283">
+        <v>6</v>
+      </c>
+      <c r="F283" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>429</v>
+        <v>352</v>
       </c>
       <c r="B284">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="C284" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D284">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="B285">
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="C285" t="s">
         <v>36</v>
       </c>
       <c r="D285">
-        <v>9.9</v>
+        <v>6</v>
+      </c>
+      <c r="F285" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="B286">
-        <v>1996</v>
+        <v>2017</v>
       </c>
       <c r="C286" t="s">
         <v>36</v>
       </c>
       <c r="D286">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="B287">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="C287" t="s">
         <v>36</v>
       </c>
       <c r="D287">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B288">
-        <v>1996</v>
+        <v>2015</v>
       </c>
       <c r="C288" t="s">
         <v>36</v>
       </c>
       <c r="D288">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>298</v>
+        <v>85</v>
       </c>
       <c r="B289">
-        <v>1996</v>
+        <v>2015</v>
       </c>
       <c r="C289" t="s">
         <v>36</v>
       </c>
       <c r="D289">
-        <v>7</v>
-      </c>
-      <c r="F289" t="s">
-        <v>479</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="B290">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="C290" t="s">
         <v>36</v>
       </c>
-      <c r="D290" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E290" s="4"/>
+      <c r="D290">
+        <v>6</v>
+      </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>332</v>
+        <v>190</v>
       </c>
       <c r="B291">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="C291" t="s">
         <v>36</v>
       </c>
-      <c r="D291" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E291" s="4"/>
+      <c r="D291">
+        <v>6</v>
+      </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>286</v>
+        <v>233</v>
       </c>
       <c r="B292">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="C292" t="s">
         <v>36</v>
       </c>
-      <c r="D292" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E292" s="4"/>
+      <c r="D292">
+        <v>6</v>
+      </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>418</v>
+        <v>123</v>
       </c>
       <c r="B293">
-        <v>1996</v>
+        <v>2012</v>
       </c>
       <c r="C293" t="s">
         <v>36</v>
       </c>
       <c r="D293">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="B294">
-        <v>1995</v>
+        <v>2012</v>
       </c>
       <c r="C294" t="s">
         <v>36</v>
       </c>
       <c r="D294">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B295">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="C295" t="s">
         <v>36</v>
       </c>
       <c r="D295">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B296">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="C296" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D296">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="B297">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="C297" t="s">
         <v>36</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="F297" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>239</v>
+        <v>399</v>
       </c>
       <c r="B298">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="C298" t="s">
         <v>36</v>
       </c>
       <c r="D298">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F298" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="B299">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="C299" t="s">
         <v>36</v>
       </c>
       <c r="D299">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F299" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B300">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="C300" t="s">
         <v>36</v>
       </c>
-      <c r="D300" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E300" s="4"/>
+      <c r="D300">
+        <v>6</v>
+      </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>428</v>
+        <v>134</v>
       </c>
       <c r="B301">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="C301" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D301">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="B302">
-        <v>1994</v>
+        <v>1965</v>
       </c>
       <c r="C302" t="s">
         <v>36</v>
       </c>
       <c r="D302">
-        <v>9.6</v>
+        <v>6</v>
+      </c>
+      <c r="F302" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>54</v>
+        <v>508</v>
       </c>
       <c r="B303">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C303" t="s">
         <v>36</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>5.5</v>
+      </c>
+      <c r="F303" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B304">
-        <v>1994</v>
+        <v>2009</v>
       </c>
       <c r="C304" t="s">
         <v>36</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="B305">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="C305" t="s">
         <v>36</v>
       </c>
       <c r="D305">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="B306">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="C306" t="s">
         <v>36</v>
       </c>
-      <c r="D306" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E306" s="4"/>
+      <c r="D306">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>277</v>
+        <v>434</v>
       </c>
       <c r="B307">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="C307" t="s">
+        <v>36</v>
+      </c>
+      <c r="D307">
         <v>5</v>
       </c>
-      <c r="D307" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E307" s="4"/>
+      <c r="F307" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B308">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="C308" t="s">
         <v>36</v>
       </c>
       <c r="D308">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="F308" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>56</v>
+        <v>410</v>
       </c>
       <c r="B309">
-        <v>1993</v>
+        <v>2024</v>
       </c>
       <c r="C309" t="s">
         <v>36</v>
       </c>
       <c r="D309">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="F309" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="B310">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C310" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D310">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B311">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="C311" t="s">
         <v>36</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>331</v>
+        <v>177</v>
       </c>
       <c r="B312">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="C312" t="s">
         <v>36</v>
       </c>
       <c r="D312">
-        <v>7</v>
-      </c>
-      <c r="F312" t="s">
-        <v>470</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="B313">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C313" t="s">
         <v>36</v>
       </c>
-      <c r="D313" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E313" s="4"/>
+      <c r="D313">
+        <v>5</v>
+      </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>357</v>
+        <v>100</v>
       </c>
       <c r="B314">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="C314" t="s">
         <v>36</v>
       </c>
-      <c r="D314" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E314" s="4"/>
+      <c r="D314">
+        <v>5</v>
+      </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>262</v>
+        <v>106</v>
       </c>
       <c r="B315">
-        <v>1993</v>
+        <v>2012</v>
       </c>
       <c r="C315" t="s">
         <v>36</v>
       </c>
-      <c r="D315" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E315" s="4"/>
+      <c r="D315">
+        <v>5</v>
+      </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>355</v>
+        <v>404</v>
       </c>
       <c r="B316">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="C316" t="s">
+        <v>36</v>
+      </c>
+      <c r="D316">
         <v>5</v>
       </c>
-      <c r="D316" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E316" s="4"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>414</v>
+        <v>250</v>
       </c>
       <c r="B317">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="C317" t="s">
         <v>36</v>
@@ -6814,1759 +6745,1621 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="B318">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="C318" t="s">
         <v>36</v>
       </c>
       <c r="D318">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>368</v>
+        <v>414</v>
       </c>
       <c r="B319">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C319" t="s">
         <v>36</v>
       </c>
       <c r="D319">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>402</v>
+        <v>270</v>
       </c>
       <c r="B320">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="C320" t="s">
         <v>36</v>
       </c>
-      <c r="D320" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E320" s="4"/>
+      <c r="D320">
+        <v>4.5</v>
+      </c>
+      <c r="F320" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="B321">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="C321" t="s">
-        <v>5</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E321" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D321">
+        <v>4.5</v>
+      </c>
+      <c r="F321" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>33</v>
+        <v>304</v>
       </c>
       <c r="B322">
-        <v>1991</v>
+        <v>2018</v>
       </c>
       <c r="C322" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>4.5</v>
+      </c>
+      <c r="F322" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="B323">
-        <v>1991</v>
+        <v>2008</v>
       </c>
       <c r="C323" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B324">
-        <v>1991</v>
+        <v>2006</v>
       </c>
       <c r="C324" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D324">
-        <v>8</v>
+        <v>4.5</v>
+      </c>
+      <c r="F324" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>309</v>
+        <v>221</v>
       </c>
       <c r="B325">
-        <v>1991</v>
+        <v>2024</v>
       </c>
       <c r="C325" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D325">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="F325" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>274</v>
+        <v>132</v>
       </c>
       <c r="B326">
-        <v>1991</v>
+        <v>2017</v>
       </c>
       <c r="C326" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D326">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F326" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B327">
-        <v>1990</v>
+        <v>2016</v>
       </c>
       <c r="C327" t="s">
         <v>36</v>
       </c>
       <c r="D327">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="F327" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>126</v>
+        <v>442</v>
       </c>
       <c r="B328">
-        <v>1990</v>
+        <v>2024</v>
       </c>
       <c r="C328" t="s">
         <v>36</v>
       </c>
       <c r="D328">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>341</v>
+        <v>184</v>
       </c>
       <c r="B329">
-        <v>1990</v>
+        <v>2017</v>
       </c>
       <c r="C329" t="s">
         <v>36</v>
       </c>
       <c r="D329">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F329" t="s">
-        <v>450</v>
+        <v>509</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="B330">
-        <v>1990</v>
+        <v>2013</v>
       </c>
       <c r="C330" t="s">
         <v>36</v>
       </c>
       <c r="D330">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F330" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="B331">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="C331" t="s">
         <v>36</v>
       </c>
       <c r="D331">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="B332">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="C332" t="s">
-        <v>36</v>
-      </c>
-      <c r="D332">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D332" s="4"/>
+      <c r="E332" s="4"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B333">
-        <v>1990</v>
+        <v>2021</v>
       </c>
       <c r="C333" t="s">
         <v>36</v>
       </c>
-      <c r="D333">
-        <v>7.5</v>
-      </c>
+      <c r="D333" s="4"/>
+      <c r="E333" s="4"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>375</v>
+        <v>25</v>
       </c>
       <c r="B334">
-        <v>1990</v>
+        <v>2021</v>
       </c>
       <c r="C334" t="s">
-        <v>36</v>
-      </c>
-      <c r="D334">
-        <v>7.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D334" s="4"/>
+      <c r="E334" s="4"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>267</v>
+      <c r="A335" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="B335">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="C335" t="s">
         <v>36</v>
       </c>
-      <c r="D335">
-        <v>6.5</v>
-      </c>
-      <c r="F335" t="s">
-        <v>451</v>
-      </c>
+      <c r="D335" s="4"/>
+      <c r="E335" s="4"/>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>387</v>
+        <v>264</v>
       </c>
       <c r="B336">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="C336" t="s">
-        <v>36</v>
-      </c>
-      <c r="D336" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D336" s="4"/>
       <c r="E336" s="4"/>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>89</v>
+        <v>371</v>
       </c>
       <c r="B337">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="C337" t="s">
         <v>36</v>
       </c>
-      <c r="D337">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D337" s="4"/>
+      <c r="E337" s="4"/>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="B338">
-        <v>1989</v>
+        <v>2017</v>
       </c>
       <c r="C338" t="s">
-        <v>36</v>
-      </c>
-      <c r="D338">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D338" s="4"/>
+      <c r="E338" s="4"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="B339">
-        <v>1989</v>
+        <v>2016</v>
       </c>
       <c r="C339" t="s">
-        <v>36</v>
-      </c>
-      <c r="D339">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>189</v>
+        <v>253</v>
       </c>
       <c r="B340">
-        <v>1989</v>
+        <v>2016</v>
       </c>
       <c r="C340" t="s">
         <v>36</v>
       </c>
-      <c r="D340">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D340" s="4"/>
+      <c r="E340" s="4"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="B341">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="C341" t="s">
         <v>36</v>
       </c>
-      <c r="D341">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D341" s="4"/>
+      <c r="E341" s="4"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>382</v>
+        <v>227</v>
       </c>
       <c r="B342">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="C342" t="s">
         <v>36</v>
       </c>
-      <c r="D342">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D342" s="4"/>
+      <c r="E342" s="4"/>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="B343">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="C343" t="s">
-        <v>36</v>
-      </c>
-      <c r="D343" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D343" s="4"/>
       <c r="E343" s="4"/>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="B344">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="C344" t="s">
         <v>36</v>
       </c>
-      <c r="D344" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D344" s="4"/>
       <c r="E344" s="4"/>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>538</v>
+        <v>283</v>
       </c>
       <c r="B345">
-        <v>1988</v>
+        <v>2015</v>
       </c>
       <c r="C345" t="s">
         <v>36</v>
       </c>
-      <c r="D345">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D345" s="4"/>
+      <c r="E345" s="4"/>
+      <c r="F345" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B346">
-        <v>1988</v>
+        <v>2014</v>
       </c>
       <c r="C346" t="s">
         <v>36</v>
       </c>
-      <c r="D346">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D346" s="4"/>
+      <c r="E346" s="4"/>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>229</v>
+        <v>279</v>
       </c>
       <c r="B347">
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="C347" t="s">
         <v>36</v>
       </c>
-      <c r="D347">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D347" s="4"/>
+      <c r="E347" s="4"/>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>378</v>
+        <v>146</v>
       </c>
       <c r="B348">
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="C348" t="s">
         <v>36</v>
       </c>
-      <c r="D348">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D348" s="4"/>
+      <c r="E348" s="4"/>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B349">
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="C349" t="s">
-        <v>27</v>
-      </c>
-      <c r="D349">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D349" s="4"/>
+      <c r="E349" s="4"/>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="B350">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="C350" t="s">
-        <v>5</v>
-      </c>
-      <c r="D350" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D350" s="4"/>
       <c r="E350" s="4"/>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>535</v>
+        <v>317</v>
       </c>
       <c r="B351">
-        <v>1988</v>
+        <v>2011</v>
       </c>
       <c r="C351" t="s">
         <v>36</v>
       </c>
-      <c r="D351" s="4">
-        <v>7</v>
-      </c>
+      <c r="D351" s="4"/>
       <c r="E351" s="4"/>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="B352">
-        <v>1987</v>
+        <v>2011</v>
       </c>
       <c r="C352" t="s">
         <v>36</v>
       </c>
-      <c r="D352">
-        <v>9.9</v>
-      </c>
+      <c r="D352" s="4"/>
+      <c r="E352" s="4"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="B353">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="C353" t="s">
         <v>36</v>
       </c>
-      <c r="D353">
-        <v>9</v>
-      </c>
+      <c r="D353" s="4"/>
+      <c r="E353" s="4"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>161</v>
+        <v>303</v>
       </c>
       <c r="B354">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="C354" t="s">
         <v>36</v>
       </c>
-      <c r="D354">
-        <v>7.6</v>
-      </c>
+      <c r="D354" s="4"/>
+      <c r="E354" s="4"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="B355">
-        <v>1987</v>
+        <v>2008</v>
       </c>
       <c r="C355" t="s">
         <v>36</v>
       </c>
-      <c r="D355">
-        <v>7</v>
-      </c>
+      <c r="D355" s="4"/>
+      <c r="E355" s="4"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>152</v>
+        <v>391</v>
       </c>
       <c r="B356">
-        <v>1987</v>
+        <v>2008</v>
       </c>
       <c r="C356" t="s">
         <v>36</v>
       </c>
-      <c r="D356" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D356" s="4"/>
       <c r="E356" s="4"/>
+      <c r="F356" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="B357">
-        <v>1986</v>
+        <v>2007</v>
       </c>
       <c r="C357" t="s">
-        <v>36</v>
-      </c>
-      <c r="D357">
-        <v>9.9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D357" s="4"/>
+      <c r="E357" s="4"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="B358">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C358" t="s">
-        <v>36</v>
-      </c>
-      <c r="D358">
-        <v>9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D358" s="4"/>
+      <c r="E358" s="4"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="B359">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C359" t="s">
         <v>36</v>
       </c>
-      <c r="D359">
-        <v>7.5</v>
-      </c>
+      <c r="D359" s="4"/>
+      <c r="E359" s="4"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>377</v>
+        <v>14</v>
       </c>
       <c r="B360">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C360" t="s">
-        <v>36</v>
-      </c>
-      <c r="D360">
-        <v>7</v>
-      </c>
-      <c r="F360" t="s">
-        <v>431</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D360" s="4"/>
+      <c r="E360" s="4"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="B361">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C361" t="s">
         <v>36</v>
       </c>
-      <c r="D361" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D361" s="4"/>
       <c r="E361" s="4"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>137</v>
+        <v>307</v>
       </c>
       <c r="B362">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C362" t="s">
-        <v>5</v>
-      </c>
-      <c r="D362" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D362" s="4"/>
       <c r="E362" s="4"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B363">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
       </c>
-      <c r="D363" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D363" s="4"/>
       <c r="E363" s="4"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>534</v>
+        <v>396</v>
       </c>
       <c r="B364">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="C364" t="s">
         <v>36</v>
       </c>
-      <c r="D364" s="4">
-        <v>7.5</v>
-      </c>
+      <c r="D364" s="4"/>
       <c r="E364" s="4"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>48</v>
+        <v>236</v>
       </c>
       <c r="B365">
-        <v>1985</v>
+        <v>2005</v>
       </c>
       <c r="C365" t="s">
-        <v>36</v>
-      </c>
-      <c r="D365">
-        <v>9.9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D365" s="4"/>
+      <c r="E365" s="4"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>256</v>
+        <v>22</v>
       </c>
       <c r="B366">
-        <v>1985</v>
+        <v>2005</v>
       </c>
       <c r="C366" t="s">
-        <v>36</v>
-      </c>
-      <c r="D366">
-        <v>7.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D366" s="4"/>
+      <c r="E366" s="4"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B367">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="C367" t="s">
-        <v>27</v>
-      </c>
-      <c r="D367">
-        <v>7</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D367" s="4"/>
+      <c r="E367" s="4"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
       <c r="B368">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="C368" t="s">
-        <v>5</v>
-      </c>
-      <c r="D368" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D368" s="4"/>
       <c r="E368" s="4"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>259</v>
+        <v>356</v>
       </c>
       <c r="B369">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="C369" t="s">
-        <v>5</v>
-      </c>
-      <c r="D369" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D369" s="4"/>
       <c r="E369" s="4"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="B370">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="C370" t="s">
         <v>36</v>
       </c>
-      <c r="D370" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D370" s="4"/>
       <c r="E370" s="4"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="B371">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="C371" t="s">
         <v>36</v>
       </c>
-      <c r="D371">
-        <v>9</v>
-      </c>
+      <c r="D371" s="4"/>
+      <c r="E371" s="4"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="B372">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="C372" t="s">
         <v>36</v>
       </c>
-      <c r="D372">
-        <v>9</v>
-      </c>
+      <c r="D372" s="4"/>
+      <c r="E372" s="4"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>365</v>
+        <v>210</v>
       </c>
       <c r="B373">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="C373" t="s">
         <v>36</v>
       </c>
-      <c r="D373">
-        <v>7.5</v>
-      </c>
+      <c r="D373" s="4"/>
+      <c r="E373" s="4"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B374">
-        <v>1984</v>
+        <v>2003</v>
       </c>
       <c r="C374" t="s">
         <v>36</v>
       </c>
-      <c r="D374">
-        <v>7.5</v>
-      </c>
+      <c r="D374" s="4"/>
+      <c r="E374" s="4"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>249</v>
+        <v>395</v>
       </c>
       <c r="B375">
-        <v>1984</v>
+        <v>2003</v>
       </c>
       <c r="C375" t="s">
         <v>36</v>
       </c>
-      <c r="D375">
-        <v>7</v>
-      </c>
+      <c r="D375" s="4"/>
+      <c r="E375" s="4"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>366</v>
+        <v>208</v>
       </c>
       <c r="B376">
-        <v>1984</v>
+        <v>2002</v>
       </c>
       <c r="C376" t="s">
         <v>36</v>
       </c>
-      <c r="D376" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D376" s="4"/>
       <c r="E376" s="4"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="B377">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="C377" t="s">
-        <v>36</v>
-      </c>
-      <c r="D377">
-        <v>9.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D377" s="4"/>
+      <c r="E377" s="4"/>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>383</v>
+        <v>284</v>
       </c>
       <c r="B378">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="C378" t="s">
         <v>36</v>
       </c>
-      <c r="D378" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D378" s="4"/>
       <c r="E378" s="4"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="B379">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="C379" t="s">
         <v>36</v>
       </c>
-      <c r="D379" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D379" s="4"/>
       <c r="E379" s="4"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="B380">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="C380" t="s">
-        <v>5</v>
-      </c>
-      <c r="D380" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D380" s="4"/>
       <c r="E380" s="4"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="B381">
-        <v>1982</v>
+        <v>2001</v>
       </c>
       <c r="C381" t="s">
-        <v>36</v>
-      </c>
-      <c r="D381">
-        <v>9.9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D381" s="4"/>
+      <c r="E381" s="4"/>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="B382">
-        <v>1982</v>
+        <v>2000</v>
       </c>
       <c r="C382" t="s">
         <v>36</v>
       </c>
-      <c r="D382">
-        <v>9.6</v>
-      </c>
+      <c r="D382" s="4"/>
+      <c r="E382" s="4"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="B383">
-        <v>1982</v>
+        <v>2000</v>
       </c>
       <c r="C383" t="s">
-        <v>5</v>
-      </c>
-      <c r="D383" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D383" s="4"/>
       <c r="E383" s="4"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="B384">
-        <v>1982</v>
+        <v>1999</v>
       </c>
       <c r="C384" t="s">
         <v>36</v>
       </c>
-      <c r="D384" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D384" s="4"/>
       <c r="E384" s="4"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B385">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="C385" t="s">
         <v>36</v>
       </c>
-      <c r="D385" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D385" s="4"/>
       <c r="E385" s="4"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B386">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
       </c>
-      <c r="D386" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D386" s="4"/>
       <c r="E386" s="4"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>536</v>
+        <v>329</v>
       </c>
       <c r="B387">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="C387" t="s">
         <v>36</v>
       </c>
-      <c r="D387" s="4">
-        <v>7.5</v>
-      </c>
+      <c r="D387" s="4"/>
       <c r="E387" s="4"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>110</v>
+        <v>297</v>
       </c>
       <c r="B388">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="C388" t="s">
         <v>36</v>
       </c>
-      <c r="D388">
-        <v>9.9</v>
-      </c>
+      <c r="D388" s="4"/>
+      <c r="E388" s="4"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>159</v>
+        <v>332</v>
       </c>
       <c r="B389">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="C389" t="s">
         <v>36</v>
       </c>
-      <c r="D389" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D389" s="4"/>
       <c r="E389" s="4"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>344</v>
+        <v>286</v>
       </c>
       <c r="B390">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="C390" t="s">
         <v>36</v>
       </c>
-      <c r="D390" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D390" s="4"/>
       <c r="E390" s="4"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="B391">
-        <v>1981</v>
+        <v>1995</v>
       </c>
       <c r="C391" t="s">
         <v>36</v>
       </c>
-      <c r="D391" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D391" s="4"/>
       <c r="E391" s="4"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="B392">
-        <v>1980</v>
+        <v>1994</v>
       </c>
       <c r="C392" t="s">
         <v>36</v>
       </c>
-      <c r="D392">
-        <v>10</v>
-      </c>
+      <c r="D392" s="4"/>
+      <c r="E392" s="4"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="B393">
-        <v>1980</v>
+        <v>1994</v>
       </c>
       <c r="C393" t="s">
-        <v>36</v>
-      </c>
-      <c r="D393">
-        <v>9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D393" s="4"/>
+      <c r="E393" s="4"/>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="B394">
-        <v>1980</v>
+        <v>1993</v>
       </c>
       <c r="C394" t="s">
         <v>36</v>
       </c>
-      <c r="D394">
-        <v>7.5</v>
-      </c>
+      <c r="D394" s="4"/>
+      <c r="E394" s="4"/>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>46</v>
+        <v>357</v>
       </c>
       <c r="B395">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="C395" t="s">
         <v>36</v>
       </c>
-      <c r="D395">
-        <v>9.9</v>
-      </c>
+      <c r="D395" s="4"/>
+      <c r="E395" s="4"/>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="B396">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="C396" t="s">
         <v>36</v>
       </c>
-      <c r="D396">
-        <v>8.3000000000000007</v>
-      </c>
+      <c r="D396" s="4"/>
+      <c r="E396" s="4"/>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="B397">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="C397" t="s">
-        <v>36</v>
-      </c>
-      <c r="D397">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D397" s="4"/>
+      <c r="E397" s="4"/>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>199</v>
+        <v>402</v>
       </c>
       <c r="B398">
-        <v>1979</v>
+        <v>1992</v>
       </c>
       <c r="C398" t="s">
         <v>36</v>
       </c>
-      <c r="D398" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D398" s="4"/>
       <c r="E398" s="4"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>360</v>
+        <v>158</v>
       </c>
       <c r="B399">
-        <v>1979</v>
+        <v>1992</v>
       </c>
       <c r="C399" t="s">
-        <v>36</v>
-      </c>
-      <c r="D399" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D399" s="4"/>
       <c r="E399" s="4"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>541</v>
+        <v>387</v>
       </c>
       <c r="B400">
-        <v>1979</v>
+        <v>1990</v>
       </c>
       <c r="C400" t="s">
-        <v>27</v>
-      </c>
-      <c r="D400">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D400" s="4"/>
+      <c r="E400" s="4"/>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>322</v>
+        <v>364</v>
       </c>
       <c r="B401">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="C401" t="s">
         <v>36</v>
       </c>
-      <c r="D401">
-        <v>7.5</v>
-      </c>
-      <c r="F401" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D401" s="4"/>
+      <c r="E401" s="4"/>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>345</v>
+        <v>118</v>
       </c>
       <c r="B402">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="C402" t="s">
         <v>36</v>
       </c>
-      <c r="D402">
-        <v>7</v>
-      </c>
-      <c r="F402" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D402" s="4"/>
+      <c r="E402" s="4"/>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>409</v>
+        <v>23</v>
       </c>
       <c r="B403">
-        <v>1978</v>
+        <v>1988</v>
       </c>
       <c r="C403" t="s">
-        <v>36</v>
-      </c>
-      <c r="D403">
-        <v>8</v>
-      </c>
-      <c r="F403" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D403" s="4"/>
+      <c r="E403" s="4"/>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="B404">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="C404" t="s">
         <v>36</v>
       </c>
-      <c r="D404">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D404" s="4"/>
+      <c r="E404" s="4"/>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>537</v>
+        <v>296</v>
       </c>
       <c r="B405">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="C405" t="s">
         <v>36</v>
       </c>
-      <c r="D405">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D405" s="4"/>
+      <c r="E405" s="4"/>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="B406">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
       </c>
-      <c r="D406" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D406" s="4"/>
       <c r="E406" s="4"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>361</v>
+        <v>308</v>
       </c>
       <c r="B407">
-        <v>1976</v>
+        <v>1986</v>
       </c>
       <c r="C407" t="s">
-        <v>36</v>
-      </c>
-      <c r="D407">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D407" s="4"/>
+      <c r="E407" s="4"/>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="B408">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="C408" t="s">
-        <v>36</v>
-      </c>
-      <c r="D408" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D408" s="4"/>
       <c r="E408" s="4"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="B409">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="C409" t="s">
-        <v>36</v>
-      </c>
-      <c r="D409">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D409" s="4"/>
+      <c r="E409" s="4"/>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>266</v>
+        <v>136</v>
       </c>
       <c r="B410">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="C410" t="s">
         <v>36</v>
       </c>
-      <c r="D410">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D410" s="4"/>
+      <c r="E410" s="4"/>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="B411">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="C411" t="s">
         <v>36</v>
       </c>
-      <c r="D411">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D411" s="4"/>
+      <c r="E411" s="4"/>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>45</v>
+        <v>383</v>
       </c>
       <c r="B412">
-        <v>1974</v>
+        <v>1983</v>
       </c>
       <c r="C412" t="s">
         <v>36</v>
       </c>
-      <c r="D412">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D412" s="4"/>
+      <c r="E412" s="4"/>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="B413">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="C413" t="s">
+        <v>36</v>
+      </c>
+      <c r="D413" s="4"/>
+      <c r="E413" s="4"/>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>17</v>
+      </c>
+      <c r="B414">
+        <v>1983</v>
+      </c>
+      <c r="C414" t="s">
         <v>5</v>
       </c>
-      <c r="D413" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E413" s="4"/>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>179</v>
-      </c>
-      <c r="B414">
-        <v>1973</v>
-      </c>
-      <c r="C414" t="s">
-        <v>36</v>
-      </c>
-      <c r="D414" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D414" s="4"/>
       <c r="E414" s="4"/>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="B415">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="C415" t="s">
-        <v>36</v>
-      </c>
-      <c r="D415" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D415" s="4"/>
       <c r="E415" s="4"/>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>38</v>
+        <v>367</v>
       </c>
       <c r="B416">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="C416" t="s">
         <v>36</v>
       </c>
-      <c r="D416">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D416" s="4"/>
+      <c r="E416" s="4"/>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="B417">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="C417" t="s">
         <v>36</v>
       </c>
-      <c r="D417">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D417" s="4"/>
+      <c r="E417" s="4"/>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B418">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="C418" t="s">
-        <v>36</v>
-      </c>
-      <c r="D418">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D418" s="4"/>
+      <c r="E418" s="4"/>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>337</v>
+        <v>159</v>
       </c>
       <c r="B419">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="C419" t="s">
         <v>36</v>
       </c>
-      <c r="D419">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D419" s="4"/>
+      <c r="E419" s="4"/>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>70</v>
+        <v>344</v>
       </c>
       <c r="B420">
-        <v>1968</v>
+        <v>1981</v>
       </c>
       <c r="C420" t="s">
         <v>36</v>
       </c>
-      <c r="D420">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D420" s="4"/>
+      <c r="E420" s="4"/>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="B421">
-        <v>1968</v>
+        <v>1981</v>
       </c>
       <c r="C421" t="s">
-        <v>5</v>
-      </c>
-      <c r="D421" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D421" s="4"/>
       <c r="E421" s="4"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="B422">
-        <v>1968</v>
+        <v>1979</v>
       </c>
       <c r="C422" t="s">
         <v>36</v>
       </c>
-      <c r="D422" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D422" s="4"/>
       <c r="E422" s="4"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="B423">
-        <v>1968</v>
+        <v>1979</v>
       </c>
       <c r="C423" t="s">
-        <v>5</v>
-      </c>
-      <c r="D423" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D423" s="4"/>
       <c r="E423" s="4"/>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B424">
-        <v>1966</v>
+        <v>1977</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
       </c>
-      <c r="D424">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D424" s="4"/>
+      <c r="E424" s="4"/>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B425">
-        <v>1965</v>
+        <v>1976</v>
       </c>
       <c r="C425" t="s">
         <v>36</v>
       </c>
-      <c r="D425">
+      <c r="D425" s="4"/>
+      <c r="E425" s="4"/>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>335</v>
+      </c>
+      <c r="B426">
+        <v>1973</v>
+      </c>
+      <c r="C426" t="s">
+        <v>5</v>
+      </c>
+      <c r="D426" s="4"/>
+      <c r="E426" s="4"/>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>179</v>
+      </c>
+      <c r="B427">
+        <v>1973</v>
+      </c>
+      <c r="C427" t="s">
+        <v>36</v>
+      </c>
+      <c r="D427" s="4"/>
+      <c r="E427" s="4"/>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>242</v>
+      </c>
+      <c r="B428">
+        <v>1973</v>
+      </c>
+      <c r="C428" t="s">
+        <v>36</v>
+      </c>
+      <c r="D428" s="4"/>
+      <c r="E428" s="4"/>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
         <v>6</v>
       </c>
-      <c r="F425" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
-        <v>358</v>
-      </c>
-      <c r="B426">
-        <v>1963</v>
-      </c>
-      <c r="C426" t="s">
-        <v>36</v>
-      </c>
-      <c r="D426">
-        <v>7</v>
-      </c>
-      <c r="F426" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
-        <v>19</v>
-      </c>
-      <c r="B427">
-        <v>1963</v>
-      </c>
-      <c r="C427" t="s">
+      <c r="B429">
+        <v>1968</v>
+      </c>
+      <c r="C429" t="s">
         <v>5</v>
       </c>
-      <c r="D427" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E427" s="4"/>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
-        <v>129</v>
-      </c>
-      <c r="B428">
-        <v>1962</v>
-      </c>
-      <c r="C428" t="s">
-        <v>36</v>
-      </c>
-      <c r="D428">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>95</v>
-      </c>
-      <c r="B429">
-        <v>1960</v>
-      </c>
-      <c r="C429" t="s">
-        <v>36</v>
-      </c>
-      <c r="D429">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D429" s="4"/>
+      <c r="E429" s="4"/>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="B430">
-        <v>1959</v>
+        <v>1968</v>
       </c>
       <c r="C430" t="s">
         <v>36</v>
       </c>
-      <c r="D430">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D430" s="4"/>
+      <c r="E430" s="4"/>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>4</v>
+        <v>390</v>
       </c>
       <c r="B431">
-        <v>1957</v>
+        <v>1968</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
       </c>
-      <c r="D431" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D431" s="4"/>
       <c r="E431" s="4"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B432">
-        <v>1954</v>
+        <v>1963</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
       </c>
-      <c r="D432" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D432" s="4"/>
       <c r="E432" s="4"/>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B433">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
       </c>
-      <c r="D433" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D433" s="4"/>
       <c r="E433" s="4"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="B434">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
       </c>
-      <c r="D434" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D434" s="4"/>
       <c r="E434" s="4"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>265</v>
+        <v>11</v>
       </c>
       <c r="B435">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
       </c>
-      <c r="D435" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="D435" s="4"/>
       <c r="E435" s="4"/>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B436">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
       </c>
-      <c r="D436">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D436" s="4"/>
+      <c r="E436" s="4"/>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="B437">
-        <v>1939</v>
+        <v>1950</v>
       </c>
       <c r="C437" t="s">
-        <v>36</v>
-      </c>
-      <c r="D437">
-        <v>9</v>
-      </c>
-      <c r="F437" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D437" s="4"/>
+      <c r="E437" s="4"/>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F437">
+      <sortCondition descending="1" ref="D1"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A217:H401">
     <sortCondition ref="A217:A401"/>
   </sortState>
@@ -8865,7 +8658,7 @@
         <v>5.5</v>
       </c>
       <c r="D32" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -8936,7 +8729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0286DF-BEF1-454C-9305-0F4D87165227}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -8946,13 +8739,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1984</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -8962,7 +8777,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CA9B39-F148-4282-B30F-098DCE817F14}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
@@ -8972,29 +8787,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B3" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
